--- a/Outputs/tables/Tablas_Mejoradas_Sectores_CON_FORMULAS.xlsx
+++ b/Outputs/tables/Tablas_Mejoradas_Sectores_CON_FORMULAS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorge\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorge\Documents\Trabajo-Profesional\Javeriana\Outputs\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA4B43F-3426-461C-9979-FC73C5C9F692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E476358-6DD3-4FE9-8239-744514A2A172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Resumen Ejecutivo" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,9 @@
     <sheet name="6. Productividad" sheetId="6" r:id="rId6"/>
     <sheet name="0. Datos Originales" sheetId="7" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5. EAM vs GEIH'!$A$1:$J$21</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="78">
   <si>
     <t>Sector</t>
   </si>
@@ -197,12 +200,6 @@
     <t>VA (millones)</t>
   </si>
   <si>
-    <t>Productividad (VA/Trabajador)</t>
-  </si>
-  <si>
-    <t>VA por Establecimiento (millones)</t>
-  </si>
-  <si>
     <t>VA_EAM</t>
   </si>
   <si>
@@ -270,19 +267,30 @@
   </si>
   <si>
     <t>Mensual_GEIH</t>
+  </si>
+  <si>
+    <t>VA por establecimiento</t>
+  </si>
+  <si>
+    <t>Productividad (VA/Trabajador) millones</t>
+  </si>
+  <si>
+    <t>ProductividaMensual</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="6">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="\$#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0&quot; mill&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0&quot; mill&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -302,6 +310,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -317,7 +332,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -340,11 +355,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -359,15 +386,29 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
@@ -691,19 +732,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="4" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -716,17 +757,18 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="1"/>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -734,23 +776,32 @@
         <v>184924</v>
       </c>
       <c r="C2" s="3">
-        <f>41513051405/1000000</f>
-        <v>41513.051404999998</v>
+        <f>41513051405</f>
+        <v>41513051405</v>
       </c>
       <c r="D2" s="3">
+        <f>C2/B2</f>
         <v>224487.094184638</v>
       </c>
-      <c r="E2" s="4">
-        <v>49912.860391295893</v>
-      </c>
-      <c r="F2" s="3">
+      <c r="E2" s="3">
+        <f>D2/12</f>
+        <v>18707.257848719833</v>
+      </c>
+      <c r="F2" s="4">
+        <v>49912.860391295901</v>
+      </c>
+      <c r="G2" s="3">
         <v>292756.70455157763</v>
       </c>
-      <c r="G2" s="4">
+      <c r="H2" s="4">
         <v>25524950</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I2" s="10">
+        <f>(H2/1000000)/12</f>
+        <v>2.1270791666666669</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -764,17 +815,25 @@
       <c r="D3" s="3">
         <v>629422.61596565158</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
+        <f t="shared" ref="E3:E22" si="0">D3/12</f>
+        <v>52451.884663804296</v>
+      </c>
+      <c r="F3" s="4">
         <v>75908.176830722747</v>
       </c>
-      <c r="F3" s="3">
+      <c r="G3" s="3">
         <v>53982.389692664146</v>
       </c>
-      <c r="G3" s="4">
+      <c r="H3" s="4">
         <v>29436578</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I3" s="10">
+        <f t="shared" ref="I3:I22" si="1">(H3/1000000)/12</f>
+        <v>2.4530481666666666</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -788,17 +847,25 @@
       <c r="D4" s="3">
         <v>95320.220998636913</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
+        <f t="shared" si="0"/>
+        <v>7943.3517498864094</v>
+      </c>
+      <c r="F4" s="4">
         <v>45184.056675514737</v>
       </c>
-      <c r="F4" s="3">
+      <c r="G4" s="3">
         <v>33381.501019895077</v>
       </c>
-      <c r="G4" s="4">
+      <c r="H4" s="4">
         <v>24009232</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I4" s="10">
+        <f t="shared" si="1"/>
+        <v>2.0007693333333334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -812,17 +879,25 @@
       <c r="D5" s="3">
         <v>84958.040324779591</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
+        <f t="shared" si="0"/>
+        <v>7079.8366937316323</v>
+      </c>
+      <c r="F5" s="4">
         <v>38283.707910443241</v>
       </c>
-      <c r="F5" s="3">
+      <c r="G5" s="3">
         <v>156115.59936070439</v>
       </c>
-      <c r="G5" s="4">
+      <c r="H5" s="4">
         <v>20875286</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="I5" s="10">
+        <f t="shared" si="1"/>
+        <v>1.7396071666666666</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -836,17 +911,25 @@
       <c r="D6" s="3">
         <v>59906.066652678703</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
+        <f t="shared" si="0"/>
+        <v>4992.1722210565586</v>
+      </c>
+      <c r="F6" s="4">
         <v>38433.070988949497</v>
       </c>
-      <c r="F6" s="3">
+      <c r="G6" s="3">
         <v>40735.455275535583</v>
       </c>
-      <c r="G6" s="4">
+      <c r="H6" s="4">
         <v>18153898</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="I6" s="10">
+        <f t="shared" si="1"/>
+        <v>1.5128248333333334</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -860,17 +943,25 @@
       <c r="D7" s="3">
         <v>98194.396709816618</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
+        <f t="shared" si="0"/>
+        <v>8182.8663924847178</v>
+      </c>
+      <c r="F7" s="4">
         <v>41873.188781014032</v>
       </c>
-      <c r="F7" s="3">
+      <c r="G7" s="3">
         <v>7992.1848473548889</v>
       </c>
-      <c r="G7" s="4">
+      <c r="H7" s="4">
         <v>22457712</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I7" s="10">
+        <f t="shared" si="1"/>
+        <v>1.8714760000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
@@ -884,17 +975,25 @@
       <c r="D8" s="3">
         <v>288965.05531069892</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
+        <f t="shared" si="0"/>
+        <v>24080.421275891578</v>
+      </c>
+      <c r="F8" s="4">
         <v>76262.751247154549</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>36072.072888374329</v>
       </c>
-      <c r="G8" s="4">
+      <c r="H8" s="4">
         <v>41549812</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="I8" s="10">
+        <f t="shared" si="1"/>
+        <v>3.4624843333333337</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
@@ -908,17 +1007,25 @@
       <c r="D9" s="3">
         <v>132875.1057408542</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
+        <f t="shared" si="0"/>
+        <v>11072.925478404517</v>
+      </c>
+      <c r="F9" s="4">
         <v>46062.00139205969</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>14227.397269248961</v>
       </c>
-      <c r="G9" s="4">
+      <c r="H9" s="4">
         <v>22549986</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="I9" s="10">
+        <f t="shared" si="1"/>
+        <v>1.8791655</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
@@ -932,17 +1039,25 @@
       <c r="D10" s="3">
         <v>514623.95216278132</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="3">
+        <f t="shared" si="0"/>
+        <v>42885.329346898441</v>
+      </c>
+      <c r="F10" s="4">
         <v>100934.9242689665</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7219.251886844635</v>
       </c>
-      <c r="G10" s="4">
+      <c r="H10" s="4">
         <v>30195434</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I10" s="10">
+        <f t="shared" si="1"/>
+        <v>2.5162861666666667</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
@@ -956,17 +1071,25 @@
       <c r="D11" s="3">
         <v>319606.41647300532</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="3">
+        <f t="shared" si="0"/>
+        <v>26633.86803941711</v>
+      </c>
+      <c r="F11" s="4">
         <v>66036.521454312751</v>
       </c>
-      <c r="F11" s="3">
+      <c r="G11" s="3">
         <v>81296.940004348755</v>
       </c>
-      <c r="G11" s="4">
+      <c r="H11" s="4">
         <v>28205038</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="I11" s="10">
+        <f t="shared" si="1"/>
+        <v>2.350419833333333</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
@@ -980,17 +1103,25 @@
       <c r="D12" s="3">
         <v>235670.09135723431</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
+        <f t="shared" si="0"/>
+        <v>19639.174279769526</v>
+      </c>
+      <c r="F12" s="4">
         <v>70018.865941101147</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>50389.893980741501</v>
       </c>
-      <c r="G12" s="4">
+      <c r="H12" s="4">
         <v>41492988</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I12" s="10">
+        <f t="shared" si="1"/>
+        <v>3.4577489999999997</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
@@ -1004,17 +1135,25 @@
       <c r="D13" s="3">
         <v>126864.8416965732</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="3">
+        <f t="shared" si="0"/>
+        <v>10572.0701413811</v>
+      </c>
+      <c r="F13" s="4">
         <v>49338.556753580837</v>
       </c>
-      <c r="F13" s="3">
+      <c r="G13" s="3">
         <v>95304.083910703659</v>
       </c>
-      <c r="G13" s="4">
+      <c r="H13" s="4">
         <v>25629082</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I13" s="10">
+        <f t="shared" si="1"/>
+        <v>2.1357568333333332</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>19</v>
       </c>
@@ -1028,17 +1167,25 @@
       <c r="D14" s="3">
         <v>238393.2218293738</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="3">
+        <f t="shared" si="0"/>
+        <v>19866.101819114483</v>
+      </c>
+      <c r="F14" s="4">
         <v>57497.088340031543</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>65302.21913433075</v>
       </c>
-      <c r="G14" s="4">
+      <c r="H14" s="4">
         <v>32789306</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I14" s="10">
+        <f t="shared" si="1"/>
+        <v>2.7324421666666669</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
@@ -1052,17 +1199,25 @@
       <c r="D15" s="3">
         <v>281316.42432063149</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="3">
+        <f t="shared" si="0"/>
+        <v>23443.035360052625</v>
+      </c>
+      <c r="F15" s="4">
         <v>65743.378169121002</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>16507.17465925217</v>
       </c>
-      <c r="G15" s="4">
+      <c r="H15" s="4">
         <v>25457616</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="I15" s="10">
+        <f t="shared" si="1"/>
+        <v>2.1214680000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
@@ -1076,17 +1231,25 @@
       <c r="D16" s="3">
         <v>116577.7516379485</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="3">
+        <f t="shared" si="0"/>
+        <v>9714.8126364957079</v>
+      </c>
+      <c r="F16" s="4">
         <v>47414.098161456983</v>
       </c>
-      <c r="F16" s="3">
+      <c r="G16" s="3">
         <v>76325.984061479568</v>
       </c>
-      <c r="G16" s="4">
+      <c r="H16" s="4">
         <v>25333972</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I16" s="10">
+        <f t="shared" si="1"/>
+        <v>2.1111643333333334</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>22</v>
       </c>
@@ -1100,17 +1263,25 @@
       <c r="D17" s="3">
         <v>176630.21738761661</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="3">
+        <f t="shared" si="0"/>
+        <v>14719.184782301383</v>
+      </c>
+      <c r="F17" s="4">
         <v>64930.592536047501</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25539.73281955719</v>
       </c>
-      <c r="G17" s="4">
+      <c r="H17" s="4">
         <v>30489758</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I17" s="10">
+        <f t="shared" si="1"/>
+        <v>2.5408131666666667</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>23</v>
       </c>
@@ -1124,17 +1295,25 @@
       <c r="D18" s="3">
         <v>99380.090849712011</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="3">
+        <f t="shared" si="0"/>
+        <v>8281.6742374760015</v>
+      </c>
+      <c r="F18" s="4">
         <v>51268.443976010924</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>17297.38198184967</v>
       </c>
-      <c r="G18" s="4">
+      <c r="H18" s="4">
         <v>30533062</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="I18" s="10">
+        <f t="shared" si="1"/>
+        <v>2.5444218333333333</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>24</v>
       </c>
@@ -1148,17 +1327,25 @@
       <c r="D19" s="3">
         <v>74406.430947147092</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="3">
+        <f t="shared" si="0"/>
+        <v>6200.5359122622576</v>
+      </c>
+      <c r="F19" s="4">
         <v>44498.073401510082</v>
       </c>
-      <c r="F19" s="3">
+      <c r="G19" s="3">
         <v>19541.168630599979</v>
       </c>
-      <c r="G19" s="4">
+      <c r="H19" s="4">
         <v>25542742</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I19" s="10">
+        <f t="shared" si="1"/>
+        <v>2.1285618333333334</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>25</v>
       </c>
@@ -1172,17 +1359,25 @@
       <c r="D20" s="3">
         <v>178330.8260174419</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="3">
+        <f t="shared" si="0"/>
+        <v>14860.902168120158</v>
+      </c>
+      <c r="F20" s="4">
         <v>52039.719040697673</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8611.7141191959381</v>
       </c>
-      <c r="G20" s="4">
+      <c r="H20" s="4">
         <v>23311912</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I20" s="10">
+        <f t="shared" si="1"/>
+        <v>1.9426593333333333</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>26</v>
       </c>
@@ -1196,17 +1391,25 @@
       <c r="D21" s="3">
         <v>93391.932557323351</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="3">
+        <f t="shared" si="0"/>
+        <v>7782.6610464436126</v>
+      </c>
+      <c r="F21" s="4">
         <v>42506.463968179691</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>39759.545756340027</v>
       </c>
-      <c r="G21" s="4">
+      <c r="H21" s="4">
         <v>23251042</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I21" s="10">
+        <f t="shared" si="1"/>
+        <v>1.9375868333333335</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>27</v>
       </c>
@@ -1220,14 +1423,22 @@
       <c r="D22" s="3">
         <v>275093.83986558369</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="3">
+        <f t="shared" si="0"/>
+        <v>22924.486655465309</v>
+      </c>
+      <c r="F22" s="4">
         <v>62818.327276718621</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>29384.831278324131</v>
       </c>
-      <c r="G22" s="4">
+      <c r="H22" s="4">
         <v>28681332</v>
+      </c>
+      <c r="I22" s="10">
+        <f t="shared" si="1"/>
+        <v>2.3901110000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1301,7 +1512,7 @@
         <v>3121</v>
       </c>
       <c r="E3" s="5">
-        <f t="shared" ref="E2:E22" si="1">C3/B3</f>
+        <f t="shared" ref="E3:E22" si="1">C3/B3</f>
         <v>0.7518486125467122</v>
       </c>
       <c r="F3" s="5">
@@ -1813,7 +2024,7 @@
         <v>1385</v>
       </c>
       <c r="D3" s="5">
-        <f t="shared" ref="D2:D22" si="2">C3/B3</f>
+        <f t="shared" ref="D3:D22" si="2">C3/B3</f>
         <v>0.11012165063210623</v>
       </c>
       <c r="E3" s="3">
@@ -2777,17 +2988,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="8" width="15" customWidth="1"/>
+    <col min="3" max="6" width="18" customWidth="1"/>
+    <col min="7" max="8" width="20" customWidth="1"/>
+    <col min="9" max="10" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2803,606 +3014,781 @@
       <c r="E1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="1"/>
+      <c r="G1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1"/>
+      <c r="I1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="3">
+        <v>20647</v>
+      </c>
+      <c r="C2" s="4">
+        <v>76262.751247154549</v>
+      </c>
+      <c r="D2" s="3">
+        <v>36072.072888374329</v>
+      </c>
+      <c r="E2" s="4">
+        <v>41549812</v>
+      </c>
+      <c r="F2" s="4">
+        <f t="shared" ref="F2:F22" si="0">E2/12</f>
+        <v>3462484.3333333335</v>
+      </c>
+      <c r="G2" s="4">
+        <v>18000000</v>
+      </c>
+      <c r="H2" s="4">
+        <f t="shared" ref="H2:H22" si="1">G2/12</f>
+        <v>1500000</v>
+      </c>
+      <c r="I2" s="6">
+        <f t="shared" ref="I2:I22" si="2">(D2-B2)/B2</f>
+        <v>0.74708543073445677</v>
+      </c>
+      <c r="J2" s="6">
+        <f t="shared" ref="J2:J22" si="3">(E2-C2)/C2</f>
+        <v>543.82445650753095</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>31240</v>
+      </c>
+      <c r="C3" s="4">
+        <v>70018.865941101147</v>
+      </c>
+      <c r="D3" s="3">
+        <v>50389.893980741501</v>
+      </c>
+      <c r="E3" s="4">
+        <v>41492988</v>
+      </c>
+      <c r="F3" s="4">
+        <f t="shared" si="0"/>
+        <v>3457749</v>
+      </c>
+      <c r="G3" s="4">
+        <v>22584000</v>
+      </c>
+      <c r="H3" s="4">
+        <f t="shared" si="1"/>
+        <v>1882000</v>
+      </c>
+      <c r="I3" s="6">
+        <f t="shared" si="2"/>
+        <v>0.61299276506854994</v>
+      </c>
+      <c r="J3" s="6">
+        <f t="shared" si="3"/>
+        <v>591.59725850034908</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="3">
+        <v>39314</v>
+      </c>
+      <c r="C4" s="4">
+        <v>57497.088340031543</v>
+      </c>
+      <c r="D4" s="3">
+        <v>65302.21913433075</v>
+      </c>
+      <c r="E4" s="4">
+        <v>32789306</v>
+      </c>
+      <c r="F4" s="4">
+        <f t="shared" si="0"/>
+        <v>2732442.1666666665</v>
+      </c>
+      <c r="G4" s="4">
+        <v>18000000</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" si="1"/>
+        <v>1500000</v>
+      </c>
+      <c r="I4" s="6">
+        <f t="shared" si="2"/>
+        <v>0.66104235474209572</v>
+      </c>
+      <c r="J4" s="6">
+        <f t="shared" si="3"/>
+        <v>569.27767747277221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="3">
+        <v>16841</v>
+      </c>
+      <c r="C5" s="4">
+        <v>51268.443976010924</v>
+      </c>
+      <c r="D5" s="3">
+        <v>17297.38198184967</v>
+      </c>
+      <c r="E5" s="4">
+        <v>30533062</v>
+      </c>
+      <c r="F5" s="4">
+        <f t="shared" si="0"/>
+        <v>2544421.8333333335</v>
+      </c>
+      <c r="G5" s="4">
+        <v>21600000</v>
+      </c>
+      <c r="H5" s="4">
+        <f t="shared" si="1"/>
+        <v>1800000</v>
+      </c>
+      <c r="I5" s="6">
+        <f t="shared" si="2"/>
+        <v>2.709945857429312E-2</v>
+      </c>
+      <c r="J5" s="6">
+        <f t="shared" si="3"/>
+        <v>594.55273443225155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="3">
+        <v>23580</v>
+      </c>
+      <c r="C6" s="4">
+        <v>64930.592536047501</v>
+      </c>
+      <c r="D6" s="3">
+        <v>25539.73281955719</v>
+      </c>
+      <c r="E6" s="4">
+        <v>30489758</v>
+      </c>
+      <c r="F6" s="4">
+        <f t="shared" si="0"/>
+        <v>2540813.1666666665</v>
+      </c>
+      <c r="G6" s="4">
+        <v>19200000</v>
+      </c>
+      <c r="H6" s="4">
+        <f t="shared" si="1"/>
+        <v>1600000</v>
+      </c>
+      <c r="I6" s="6">
+        <f t="shared" si="2"/>
+        <v>8.3109958420576335E-2</v>
+      </c>
+      <c r="J6" s="6">
+        <f t="shared" si="3"/>
+        <v>468.57461512572843</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="3">
+        <v>7421</v>
+      </c>
+      <c r="C7" s="4">
+        <v>100934.9242689665</v>
+      </c>
+      <c r="D7" s="3">
+        <v>7219.251886844635</v>
+      </c>
+      <c r="E7" s="4">
+        <v>30195434</v>
+      </c>
+      <c r="F7" s="4">
+        <f t="shared" si="0"/>
+        <v>2516286.1666666665</v>
+      </c>
+      <c r="G7" s="4">
+        <v>18000000</v>
+      </c>
+      <c r="H7" s="4">
+        <f t="shared" si="1"/>
+        <v>1500000</v>
+      </c>
+      <c r="I7" s="6">
+        <f t="shared" si="2"/>
+        <v>-2.718610876638795E-2</v>
+      </c>
+      <c r="J7" s="6">
+        <f t="shared" si="3"/>
+        <v>298.15744444942243</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3">
+        <v>12577</v>
+      </c>
+      <c r="C8" s="4">
+        <v>75908.176830722747</v>
+      </c>
+      <c r="D8" s="3">
+        <v>53982.389692664146</v>
+      </c>
+      <c r="E8" s="4">
+        <v>29436578</v>
+      </c>
+      <c r="F8" s="4">
+        <f t="shared" si="0"/>
+        <v>2453048.1666666665</v>
+      </c>
+      <c r="G8" s="4">
+        <v>18000000</v>
+      </c>
+      <c r="H8" s="4">
+        <f t="shared" si="1"/>
+        <v>1500000</v>
+      </c>
+      <c r="I8" s="6">
+        <f t="shared" si="2"/>
+        <v>3.2921515220373814</v>
+      </c>
+      <c r="J8" s="6">
+        <f t="shared" si="3"/>
+        <v>386.79192478360204</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="3">
+        <v>59219</v>
+      </c>
+      <c r="C9" s="4">
+        <v>62818.327276718621</v>
+      </c>
+      <c r="D9" s="3">
+        <v>29384.831278324131</v>
+      </c>
+      <c r="E9" s="4">
+        <v>28681332</v>
+      </c>
+      <c r="F9" s="4">
+        <f t="shared" si="0"/>
+        <v>2390111</v>
+      </c>
+      <c r="G9" s="4">
+        <v>17760000</v>
+      </c>
+      <c r="H9" s="4">
+        <f t="shared" si="1"/>
+        <v>1480000</v>
+      </c>
+      <c r="I9" s="6">
+        <f t="shared" si="2"/>
+        <v>-0.50379386213336719</v>
+      </c>
+      <c r="J9" s="6">
+        <f t="shared" si="3"/>
+        <v>455.5758631817265</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="3">
+        <v>59382</v>
+      </c>
+      <c r="C10" s="4">
+        <v>66036.521454312751</v>
+      </c>
+      <c r="D10" s="3">
+        <v>81296.940004348755</v>
+      </c>
+      <c r="E10" s="4">
+        <v>28205038</v>
+      </c>
+      <c r="F10" s="4">
+        <f t="shared" si="0"/>
+        <v>2350419.8333333335</v>
+      </c>
+      <c r="G10" s="4">
+        <v>18000000</v>
+      </c>
+      <c r="H10" s="4">
+        <f t="shared" si="1"/>
+        <v>1500000</v>
+      </c>
+      <c r="I10" s="6">
+        <f t="shared" si="2"/>
+        <v>0.3690502173107803</v>
+      </c>
+      <c r="J10" s="6">
+        <f t="shared" si="3"/>
+        <v>426.11271549204184</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="3">
+        <v>62974</v>
+      </c>
+      <c r="C11" s="4">
+        <v>49338.556753580837</v>
+      </c>
+      <c r="D11" s="3">
+        <v>95304.083910703659</v>
+      </c>
+      <c r="E11" s="4">
+        <v>25629082</v>
+      </c>
+      <c r="F11" s="4">
+        <f t="shared" si="0"/>
+        <v>2135756.8333333335</v>
+      </c>
+      <c r="G11" s="4">
+        <v>17544000</v>
+      </c>
+      <c r="H11" s="4">
+        <f t="shared" si="1"/>
+        <v>1462000</v>
+      </c>
+      <c r="I11" s="6">
+        <f t="shared" si="2"/>
+        <v>0.51338780942458251</v>
+      </c>
+      <c r="J11" s="6">
+        <f t="shared" si="3"/>
+        <v>518.45341911810021</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="3">
+        <v>10463</v>
+      </c>
+      <c r="C12" s="4">
+        <v>44498.073401510082</v>
+      </c>
+      <c r="D12" s="3">
+        <v>19541.168630599979</v>
+      </c>
+      <c r="E12" s="4">
+        <v>25542742</v>
+      </c>
+      <c r="F12" s="4">
+        <f t="shared" si="0"/>
+        <v>2128561.8333333335</v>
+      </c>
+      <c r="G12" s="4">
+        <v>19800000</v>
+      </c>
+      <c r="H12" s="4">
+        <f t="shared" si="1"/>
+        <v>1650000</v>
+      </c>
+      <c r="I12" s="6">
+        <f t="shared" si="2"/>
+        <v>0.8676449040045856</v>
+      </c>
+      <c r="J12" s="6">
+        <f t="shared" si="3"/>
+        <v>573.01905402792522</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B13" s="3">
         <v>184924</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C13" s="4">
         <v>49912.860391295893</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D13" s="3">
         <v>292756.70455157763</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E13" s="4">
         <v>25524950</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F13" s="4">
+        <f t="shared" si="0"/>
+        <v>2127079.1666666665</v>
+      </c>
+      <c r="G13" s="4">
         <v>16800000</v>
       </c>
-      <c r="G2" s="6">
-        <f>(D2-B2)/B2</f>
+      <c r="H13" s="4">
+        <f t="shared" si="1"/>
+        <v>1400000</v>
+      </c>
+      <c r="I13" s="6">
+        <f t="shared" si="2"/>
         <v>0.58311903566642309</v>
       </c>
-      <c r="H2" s="6">
-        <f t="shared" ref="H2:H22" si="0">(E2-C2)/C2</f>
+      <c r="J13" s="6">
+        <f t="shared" si="3"/>
         <v>510.39024692023452</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3">
-        <v>12577</v>
-      </c>
-      <c r="C3" s="4">
-        <v>75908.176830722747</v>
-      </c>
-      <c r="D3" s="3">
-        <v>53982.389692664146</v>
-      </c>
-      <c r="E3" s="4">
-        <v>29436578</v>
-      </c>
-      <c r="F3" s="4">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="3">
+        <v>13174</v>
+      </c>
+      <c r="C14" s="4">
+        <v>65743.378169121002</v>
+      </c>
+      <c r="D14" s="3">
+        <v>16507.17465925217</v>
+      </c>
+      <c r="E14" s="4">
+        <v>25457616</v>
+      </c>
+      <c r="F14" s="4">
+        <f t="shared" si="0"/>
+        <v>2121468</v>
+      </c>
+      <c r="G14" s="4">
+        <v>20400000</v>
+      </c>
+      <c r="H14" s="4">
+        <f t="shared" si="1"/>
+        <v>1700000</v>
+      </c>
+      <c r="I14" s="6">
+        <f t="shared" si="2"/>
+        <v>0.25301158791955142</v>
+      </c>
+      <c r="J14" s="6">
+        <f t="shared" si="3"/>
+        <v>386.2270745581672</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="3">
+        <v>34647</v>
+      </c>
+      <c r="C15" s="4">
+        <v>47414.098161456983</v>
+      </c>
+      <c r="D15" s="3">
+        <v>76325.984061479568</v>
+      </c>
+      <c r="E15" s="4">
+        <v>25333972</v>
+      </c>
+      <c r="F15" s="4">
+        <f t="shared" si="0"/>
+        <v>2111164.3333333335</v>
+      </c>
+      <c r="G15" s="4">
+        <v>17520000</v>
+      </c>
+      <c r="H15" s="4">
+        <f t="shared" si="1"/>
+        <v>1460000</v>
+      </c>
+      <c r="I15" s="6">
+        <f t="shared" si="2"/>
+        <v>1.202960835324258</v>
+      </c>
+      <c r="J15" s="6">
+        <f t="shared" si="3"/>
+        <v>533.31306261971758</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3">
+        <v>27878</v>
+      </c>
+      <c r="C16" s="4">
+        <v>45184.056675514737</v>
+      </c>
+      <c r="D16" s="3">
+        <v>33381.501019895077</v>
+      </c>
+      <c r="E16" s="4">
+        <v>24009232</v>
+      </c>
+      <c r="F16" s="4">
+        <f t="shared" si="0"/>
+        <v>2000769.3333333333</v>
+      </c>
+      <c r="G16" s="4">
+        <v>16800000</v>
+      </c>
+      <c r="H16" s="4">
+        <f t="shared" si="1"/>
+        <v>1400000</v>
+      </c>
+      <c r="I16" s="6">
+        <f t="shared" si="2"/>
+        <v>0.19741376784184936</v>
+      </c>
+      <c r="J16" s="6">
+        <f t="shared" si="3"/>
+        <v>530.36512669546585</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="3">
+        <v>6880</v>
+      </c>
+      <c r="C17" s="4">
+        <v>52039.719040697673</v>
+      </c>
+      <c r="D17" s="3">
+        <v>8611.7141191959381</v>
+      </c>
+      <c r="E17" s="4">
+        <v>23311912</v>
+      </c>
+      <c r="F17" s="4">
+        <f t="shared" si="0"/>
+        <v>1942659.3333333333</v>
+      </c>
+      <c r="G17" s="4">
+        <v>18600000</v>
+      </c>
+      <c r="H17" s="4">
+        <f t="shared" si="1"/>
+        <v>1550000</v>
+      </c>
+      <c r="I17" s="6">
+        <f t="shared" si="2"/>
+        <v>0.25170263360406075</v>
+      </c>
+      <c r="J17" s="6">
+        <f t="shared" si="3"/>
+        <v>446.96383281333459</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="3">
+        <v>17096</v>
+      </c>
+      <c r="C18" s="4">
+        <v>42506.463968179691</v>
+      </c>
+      <c r="D18" s="3">
+        <v>39759.545756340027</v>
+      </c>
+      <c r="E18" s="4">
+        <v>23251042</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" si="0"/>
+        <v>1937586.8333333333</v>
+      </c>
+      <c r="G18" s="4">
+        <v>15600000</v>
+      </c>
+      <c r="H18" s="4">
+        <f t="shared" si="1"/>
+        <v>1300000</v>
+      </c>
+      <c r="I18" s="6">
+        <f t="shared" si="2"/>
+        <v>1.3256636497625192</v>
+      </c>
+      <c r="J18" s="6">
+        <f t="shared" si="3"/>
+        <v>546.00014608144568</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3">
+        <v>17959</v>
+      </c>
+      <c r="C19" s="4">
+        <v>46062.00139205969</v>
+      </c>
+      <c r="D19" s="3">
+        <v>14227.397269248961</v>
+      </c>
+      <c r="E19" s="4">
+        <v>22549986</v>
+      </c>
+      <c r="F19" s="4">
+        <f t="shared" si="0"/>
+        <v>1879165.5</v>
+      </c>
+      <c r="G19" s="4">
         <v>18000000</v>
       </c>
-      <c r="G3" s="6">
-        <f t="shared" ref="G2:G22" si="1">(D3-B3)/B3</f>
-        <v>3.2921515220373814</v>
-      </c>
-      <c r="H3" s="6">
-        <f t="shared" si="0"/>
-        <v>386.79192478360204</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3">
-        <v>27878</v>
-      </c>
-      <c r="C4" s="4">
-        <v>45184.056675514737</v>
-      </c>
-      <c r="D4" s="3">
-        <v>33381.501019895077</v>
-      </c>
-      <c r="E4" s="4">
-        <v>24009232</v>
-      </c>
-      <c r="F4" s="4">
-        <v>16800000</v>
-      </c>
-      <c r="G4" s="6">
-        <f t="shared" si="1"/>
-        <v>0.19741376784184936</v>
-      </c>
-      <c r="H4" s="6">
-        <f t="shared" si="0"/>
-        <v>530.36512669546585</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="H19" s="4">
+        <f t="shared" si="1"/>
+        <v>1500000</v>
+      </c>
+      <c r="I19" s="6">
+        <f t="shared" si="2"/>
+        <v>-0.20778454984971542</v>
+      </c>
+      <c r="J19" s="6">
+        <f t="shared" si="3"/>
+        <v>488.55723413023986</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="3">
+        <v>3708</v>
+      </c>
+      <c r="C20" s="4">
+        <v>41873.188781014032</v>
+      </c>
+      <c r="D20" s="3">
+        <v>7992.1848473548889</v>
+      </c>
+      <c r="E20" s="4">
+        <v>22457712</v>
+      </c>
+      <c r="F20" s="4">
+        <f t="shared" si="0"/>
+        <v>1871476</v>
+      </c>
+      <c r="G20" s="4">
+        <v>15600000</v>
+      </c>
+      <c r="H20" s="4">
+        <f t="shared" si="1"/>
+        <v>1300000</v>
+      </c>
+      <c r="I20" s="6">
+        <f t="shared" si="2"/>
+        <v>1.1553896567839506</v>
+      </c>
+      <c r="J20" s="6">
+        <f t="shared" si="3"/>
+        <v>535.32676788596245</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B21" s="3">
         <v>66014</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C21" s="4">
         <v>38283.707910443241</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D21" s="3">
         <v>156115.59936070439</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E21" s="4">
         <v>20875286</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F21" s="4">
+        <f t="shared" si="0"/>
+        <v>1739607.1666666667</v>
+      </c>
+      <c r="G21" s="4">
         <v>15600000</v>
       </c>
-      <c r="G5" s="6">
-        <f t="shared" si="1"/>
+      <c r="H21" s="4">
+        <f t="shared" si="1"/>
+        <v>1300000</v>
+      </c>
+      <c r="I21" s="6">
+        <f t="shared" si="2"/>
         <v>1.3648862265686732</v>
       </c>
-      <c r="H5" s="6">
-        <f t="shared" si="0"/>
+      <c r="J21" s="6">
+        <f t="shared" si="3"/>
         <v>544.2785829636299</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+    <row r="22" spans="1:10" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B22" s="12">
         <v>14298</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C22" s="13">
         <v>38433.070988949497</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D22" s="12">
         <v>40735.455275535583</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E22" s="13">
         <v>18153898</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F22" s="4">
+        <f t="shared" si="0"/>
+        <v>1512824.8333333333</v>
+      </c>
+      <c r="G22" s="13">
         <v>15600000</v>
       </c>
-      <c r="G6" s="6">
-        <f t="shared" si="1"/>
+      <c r="H22" s="13">
+        <f t="shared" si="1"/>
+        <v>1300000</v>
+      </c>
+      <c r="I22" s="14">
+        <f t="shared" si="2"/>
         <v>1.8490317020237503</v>
       </c>
-      <c r="H6" s="6">
-        <f t="shared" si="0"/>
+      <c r="J22" s="14">
+        <f t="shared" si="3"/>
         <v>471.35096058859608</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="3">
-        <v>3708</v>
-      </c>
-      <c r="C7" s="4">
-        <v>41873.188781014032</v>
-      </c>
-      <c r="D7" s="3">
-        <v>7992.1848473548889</v>
-      </c>
-      <c r="E7" s="4">
-        <v>22457712</v>
-      </c>
-      <c r="F7" s="4">
-        <v>15600000</v>
-      </c>
-      <c r="G7" s="6">
-        <f t="shared" si="1"/>
-        <v>1.1553896567839506</v>
-      </c>
-      <c r="H7" s="6">
-        <f t="shared" si="0"/>
-        <v>535.32676788596245</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="3">
-        <v>20647</v>
-      </c>
-      <c r="C8" s="4">
-        <v>76262.751247154549</v>
-      </c>
-      <c r="D8" s="3">
-        <v>36072.072888374329</v>
-      </c>
-      <c r="E8" s="4">
-        <v>41549812</v>
-      </c>
-      <c r="F8" s="4">
-        <v>18000000</v>
-      </c>
-      <c r="G8" s="6">
-        <f t="shared" si="1"/>
-        <v>0.74708543073445677</v>
-      </c>
-      <c r="H8" s="6">
-        <f t="shared" si="0"/>
-        <v>543.82445650753095</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="3">
-        <v>17959</v>
-      </c>
-      <c r="C9" s="4">
-        <v>46062.00139205969</v>
-      </c>
-      <c r="D9" s="3">
-        <v>14227.397269248961</v>
-      </c>
-      <c r="E9" s="4">
-        <v>22549986</v>
-      </c>
-      <c r="F9" s="4">
-        <v>18000000</v>
-      </c>
-      <c r="G9" s="6">
-        <f t="shared" si="1"/>
-        <v>-0.20778454984971542</v>
-      </c>
-      <c r="H9" s="6">
-        <f t="shared" si="0"/>
-        <v>488.55723413023986</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="3">
-        <v>7421</v>
-      </c>
-      <c r="C10" s="4">
-        <v>100934.9242689665</v>
-      </c>
-      <c r="D10" s="3">
-        <v>7219.251886844635</v>
-      </c>
-      <c r="E10" s="4">
-        <v>30195434</v>
-      </c>
-      <c r="F10" s="4">
-        <v>18000000</v>
-      </c>
-      <c r="G10" s="6">
-        <f t="shared" si="1"/>
-        <v>-2.718610876638795E-2</v>
-      </c>
-      <c r="H10" s="6">
-        <f t="shared" si="0"/>
-        <v>298.15744444942243</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="3">
-        <v>59382</v>
-      </c>
-      <c r="C11" s="4">
-        <v>66036.521454312751</v>
-      </c>
-      <c r="D11" s="3">
-        <v>81296.940004348755</v>
-      </c>
-      <c r="E11" s="4">
-        <v>28205038</v>
-      </c>
-      <c r="F11" s="4">
-        <v>18000000</v>
-      </c>
-      <c r="G11" s="6">
-        <f t="shared" si="1"/>
-        <v>0.3690502173107803</v>
-      </c>
-      <c r="H11" s="6">
-        <f t="shared" si="0"/>
-        <v>426.11271549204184</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="3">
-        <v>31240</v>
-      </c>
-      <c r="C12" s="4">
-        <v>70018.865941101147</v>
-      </c>
-      <c r="D12" s="3">
-        <v>50389.893980741501</v>
-      </c>
-      <c r="E12" s="4">
-        <v>41492988</v>
-      </c>
-      <c r="F12" s="4">
-        <v>22584000</v>
-      </c>
-      <c r="G12" s="6">
-        <f t="shared" si="1"/>
-        <v>0.61299276506854994</v>
-      </c>
-      <c r="H12" s="6">
-        <f t="shared" si="0"/>
-        <v>591.59725850034908</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="3">
-        <v>62974</v>
-      </c>
-      <c r="C13" s="4">
-        <v>49338.556753580837</v>
-      </c>
-      <c r="D13" s="3">
-        <v>95304.083910703659</v>
-      </c>
-      <c r="E13" s="4">
-        <v>25629082</v>
-      </c>
-      <c r="F13" s="4">
-        <v>17544000</v>
-      </c>
-      <c r="G13" s="6">
-        <f t="shared" si="1"/>
-        <v>0.51338780942458251</v>
-      </c>
-      <c r="H13" s="6">
-        <f t="shared" si="0"/>
-        <v>518.45341911810021</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="3">
-        <v>39314</v>
-      </c>
-      <c r="C14" s="4">
-        <v>57497.088340031543</v>
-      </c>
-      <c r="D14" s="3">
-        <v>65302.21913433075</v>
-      </c>
-      <c r="E14" s="4">
-        <v>32789306</v>
-      </c>
-      <c r="F14" s="4">
-        <v>18000000</v>
-      </c>
-      <c r="G14" s="6">
-        <f t="shared" si="1"/>
-        <v>0.66104235474209572</v>
-      </c>
-      <c r="H14" s="6">
-        <f t="shared" si="0"/>
-        <v>569.27767747277221</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="3">
-        <v>13174</v>
-      </c>
-      <c r="C15" s="4">
-        <v>65743.378169121002</v>
-      </c>
-      <c r="D15" s="3">
-        <v>16507.17465925217</v>
-      </c>
-      <c r="E15" s="4">
-        <v>25457616</v>
-      </c>
-      <c r="F15" s="4">
-        <v>20400000</v>
-      </c>
-      <c r="G15" s="6">
-        <f t="shared" si="1"/>
-        <v>0.25301158791955142</v>
-      </c>
-      <c r="H15" s="6">
-        <f t="shared" si="0"/>
-        <v>386.2270745581672</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="3">
-        <v>34647</v>
-      </c>
-      <c r="C16" s="4">
-        <v>47414.098161456983</v>
-      </c>
-      <c r="D16" s="3">
-        <v>76325.984061479568</v>
-      </c>
-      <c r="E16" s="4">
-        <v>25333972</v>
-      </c>
-      <c r="F16" s="4">
-        <v>17520000</v>
-      </c>
-      <c r="G16" s="6">
-        <f t="shared" si="1"/>
-        <v>1.202960835324258</v>
-      </c>
-      <c r="H16" s="6">
-        <f t="shared" si="0"/>
-        <v>533.31306261971758</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="3">
-        <v>23580</v>
-      </c>
-      <c r="C17" s="4">
-        <v>64930.592536047501</v>
-      </c>
-      <c r="D17" s="3">
-        <v>25539.73281955719</v>
-      </c>
-      <c r="E17" s="4">
-        <v>30489758</v>
-      </c>
-      <c r="F17" s="4">
-        <v>19200000</v>
-      </c>
-      <c r="G17" s="6">
-        <f t="shared" si="1"/>
-        <v>8.3109958420576335E-2</v>
-      </c>
-      <c r="H17" s="6">
-        <f t="shared" si="0"/>
-        <v>468.57461512572843</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="3">
-        <v>16841</v>
-      </c>
-      <c r="C18" s="4">
-        <v>51268.443976010924</v>
-      </c>
-      <c r="D18" s="3">
-        <v>17297.38198184967</v>
-      </c>
-      <c r="E18" s="4">
-        <v>30533062</v>
-      </c>
-      <c r="F18" s="4">
-        <v>21600000</v>
-      </c>
-      <c r="G18" s="6">
-        <f t="shared" si="1"/>
-        <v>2.709945857429312E-2</v>
-      </c>
-      <c r="H18" s="6">
-        <f t="shared" si="0"/>
-        <v>594.55273443225155</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="3">
-        <v>10463</v>
-      </c>
-      <c r="C19" s="4">
-        <v>44498.073401510082</v>
-      </c>
-      <c r="D19" s="3">
-        <v>19541.168630599979</v>
-      </c>
-      <c r="E19" s="4">
-        <v>25542742</v>
-      </c>
-      <c r="F19" s="4">
-        <v>19800000</v>
-      </c>
-      <c r="G19" s="6">
-        <f t="shared" si="1"/>
-        <v>0.8676449040045856</v>
-      </c>
-      <c r="H19" s="6">
-        <f t="shared" si="0"/>
-        <v>573.01905402792522</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="3">
-        <v>6880</v>
-      </c>
-      <c r="C20" s="4">
-        <v>52039.719040697673</v>
-      </c>
-      <c r="D20" s="3">
-        <v>8611.7141191959381</v>
-      </c>
-      <c r="E20" s="4">
-        <v>23311912</v>
-      </c>
-      <c r="F20" s="4">
-        <v>18600000</v>
-      </c>
-      <c r="G20" s="6">
-        <f t="shared" si="1"/>
-        <v>0.25170263360406075</v>
-      </c>
-      <c r="H20" s="6">
-        <f t="shared" si="0"/>
-        <v>446.96383281333459</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="3">
-        <v>17096</v>
-      </c>
-      <c r="C21" s="4">
-        <v>42506.463968179691</v>
-      </c>
-      <c r="D21" s="3">
-        <v>39759.545756340027</v>
-      </c>
-      <c r="E21" s="4">
-        <v>23251042</v>
-      </c>
-      <c r="F21" s="4">
-        <v>15600000</v>
-      </c>
-      <c r="G21" s="6">
-        <f t="shared" si="1"/>
-        <v>1.3256636497625192</v>
-      </c>
-      <c r="H21" s="6">
-        <f t="shared" si="0"/>
-        <v>546.00014608144568</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="3">
-        <v>59219</v>
-      </c>
-      <c r="C22" s="4">
-        <v>62818.327276718621</v>
-      </c>
-      <c r="D22" s="3">
-        <v>29384.831278324131</v>
-      </c>
-      <c r="E22" s="4">
-        <v>28681332</v>
-      </c>
-      <c r="F22" s="4">
-        <v>17760000</v>
-      </c>
-      <c r="G22" s="6">
-        <f t="shared" si="1"/>
-        <v>-0.50379386213336719</v>
-      </c>
-      <c r="H22" s="6">
-        <f t="shared" si="0"/>
-        <v>455.5758631817265</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:H22">
+  <autoFilter ref="A1:J21" xr:uid="{00000000-0001-0000-0400-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J22">
+      <sortCondition descending="1" ref="F1:F21"/>
+    </sortState>
+  </autoFilter>
+  <conditionalFormatting sqref="I2:J21">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -3416,17 +3802,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="3" width="15" customWidth="1"/>
-    <col min="4" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3436,20 +3825,24 @@
       <c r="C1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="1"/>
+      <c r="E1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -3460,22 +3853,30 @@
         <v>184924</v>
       </c>
       <c r="D2" s="3">
+        <f>C2/B2</f>
+        <v>143.68609168609169</v>
+      </c>
+      <c r="E2" s="3">
         <v>41513051405</v>
       </c>
-      <c r="E2" s="7">
-        <f t="shared" ref="E2:E22" si="0">D2/1000000</f>
+      <c r="F2" s="7">
+        <f t="shared" ref="F2:F22" si="0">E2/1000000</f>
         <v>41513.051404999998</v>
       </c>
-      <c r="F2" s="3">
-        <f>D2/C2</f>
-        <v>224487.094184638</v>
-      </c>
-      <c r="G2" s="8">
-        <f>D2/B2/1000000</f>
-        <v>32.255673197358199</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G2" s="3">
+        <f>(E2/1000)/C2</f>
+        <v>224.48709418463801</v>
+      </c>
+      <c r="H2" s="17">
+        <f>(E2/B2)/1000</f>
+        <v>32255.673197358199</v>
+      </c>
+      <c r="I2" s="15">
+        <f>G2/12</f>
+        <v>18.707257848719834</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -3486,22 +3887,30 @@
         <v>12577</v>
       </c>
       <c r="D3" s="3">
+        <f t="shared" ref="D3:D22" si="1">C3/B3</f>
+        <v>237.30188679245282</v>
+      </c>
+      <c r="E3" s="3">
         <v>7916248241</v>
       </c>
-      <c r="E3" s="7">
+      <c r="F3" s="7">
         <f t="shared" si="0"/>
         <v>7916.2482410000002</v>
       </c>
-      <c r="F3" s="3">
-        <f t="shared" ref="F2:F22" si="1">D3/C3</f>
-        <v>629422.61596565158</v>
-      </c>
-      <c r="G3" s="8">
-        <f t="shared" ref="G2:G22" si="2">D3/B3/1000000</f>
-        <v>149.36317435849057</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G3" s="3">
+        <f t="shared" ref="G3:G22" si="2">(E3/1000)/C3</f>
+        <v>629.42261596565163</v>
+      </c>
+      <c r="H3" s="17">
+        <f t="shared" ref="H3:H22" si="3">(E3/B3)/1000</f>
+        <v>149363.17435849056</v>
+      </c>
+      <c r="I3" s="15">
+        <f t="shared" ref="I3:I24" si="4">G3/12</f>
+        <v>52.4518846638043</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -3512,22 +3921,30 @@
         <v>27878</v>
       </c>
       <c r="D4" s="3">
+        <f t="shared" si="1"/>
+        <v>140.09045226130652</v>
+      </c>
+      <c r="E4" s="3">
         <v>2657337121</v>
       </c>
-      <c r="E4" s="7">
+      <c r="F4" s="7">
         <f t="shared" si="0"/>
         <v>2657.337121</v>
       </c>
-      <c r="F4" s="3">
-        <f t="shared" si="1"/>
-        <v>95320.220998636913</v>
-      </c>
-      <c r="G4" s="8">
+      <c r="G4" s="3">
         <f t="shared" si="2"/>
-        <v>13.353452869346734</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>95.320220998636913</v>
+      </c>
+      <c r="H4" s="17">
+        <f t="shared" si="3"/>
+        <v>13353.452869346735</v>
+      </c>
+      <c r="I4" s="15">
+        <f t="shared" si="4"/>
+        <v>7.9433517498864097</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -3538,22 +3955,30 @@
         <v>66014</v>
       </c>
       <c r="D5" s="3">
+        <f t="shared" si="1"/>
+        <v>109.11404958677686</v>
+      </c>
+      <c r="E5" s="3">
         <v>5608420074</v>
       </c>
-      <c r="E5" s="7">
+      <c r="F5" s="7">
         <f t="shared" si="0"/>
         <v>5608.4200739999997</v>
       </c>
-      <c r="F5" s="3">
-        <f t="shared" si="1"/>
-        <v>84958.040324779591</v>
-      </c>
-      <c r="G5" s="8">
+      <c r="G5" s="3">
         <f t="shared" si="2"/>
-        <v>9.2701158247933897</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="55.2" x14ac:dyDescent="0.3">
+        <v>84.958040324779589</v>
+      </c>
+      <c r="H5" s="17">
+        <f t="shared" si="3"/>
+        <v>9270.115824793389</v>
+      </c>
+      <c r="I5" s="15">
+        <f t="shared" si="4"/>
+        <v>7.0798366937316324</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -3564,22 +3989,30 @@
         <v>14298</v>
       </c>
       <c r="D6" s="3">
+        <f t="shared" si="1"/>
+        <v>82.172413793103445</v>
+      </c>
+      <c r="E6" s="3">
         <v>856536941</v>
       </c>
-      <c r="E6" s="7">
+      <c r="F6" s="7">
         <f t="shared" si="0"/>
         <v>856.53694099999996</v>
       </c>
-      <c r="F6" s="3">
-        <f t="shared" si="1"/>
-        <v>59906.066652678695</v>
-      </c>
-      <c r="G6" s="8">
+      <c r="G6" s="3">
         <f t="shared" si="2"/>
-        <v>4.9226260977011487</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+        <v>59.906066652678696</v>
+      </c>
+      <c r="H6" s="17">
+        <f t="shared" si="3"/>
+        <v>4922.6260977011489</v>
+      </c>
+      <c r="I6" s="15">
+        <f t="shared" si="4"/>
+        <v>4.992172221056558</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -3590,22 +4023,30 @@
         <v>3708</v>
       </c>
       <c r="D7" s="3">
+        <f t="shared" si="1"/>
+        <v>41.662921348314605</v>
+      </c>
+      <c r="E7" s="3">
         <v>364104823</v>
       </c>
-      <c r="E7" s="7">
+      <c r="F7" s="7">
         <f t="shared" si="0"/>
         <v>364.10482300000001</v>
       </c>
-      <c r="F7" s="3">
-        <f t="shared" si="1"/>
-        <v>98194.396709816618</v>
-      </c>
-      <c r="G7" s="8">
+      <c r="G7" s="3">
         <f t="shared" si="2"/>
-        <v>4.0910654269662921</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.194396709816601</v>
+      </c>
+      <c r="H7" s="17">
+        <f t="shared" si="3"/>
+        <v>4091.0654269662923</v>
+      </c>
+      <c r="I7" s="15">
+        <f t="shared" si="4"/>
+        <v>8.1828663924847174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
@@ -3616,22 +4057,30 @@
         <v>20647</v>
       </c>
       <c r="D8" s="3">
+        <f t="shared" si="1"/>
+        <v>158.82307692307691</v>
+      </c>
+      <c r="E8" s="3">
         <v>5966261497</v>
       </c>
-      <c r="E8" s="7">
+      <c r="F8" s="7">
         <f t="shared" si="0"/>
         <v>5966.2614970000004</v>
       </c>
-      <c r="F8" s="3">
-        <f t="shared" si="1"/>
-        <v>288965.05531069887</v>
-      </c>
-      <c r="G8" s="8">
+      <c r="G8" s="3">
         <f t="shared" si="2"/>
-        <v>45.894319207692313</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+        <v>288.96505531069892</v>
+      </c>
+      <c r="H8" s="17">
+        <f t="shared" si="3"/>
+        <v>45894.319207692308</v>
+      </c>
+      <c r="I8" s="15">
+        <f t="shared" si="4"/>
+        <v>24.080421275891577</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
@@ -3642,22 +4091,30 @@
         <v>17959</v>
       </c>
       <c r="D9" s="3">
+        <f t="shared" si="1"/>
+        <v>60.265100671140942</v>
+      </c>
+      <c r="E9" s="3">
         <v>2386304024</v>
       </c>
-      <c r="E9" s="7">
+      <c r="F9" s="7">
         <f t="shared" si="0"/>
         <v>2386.304024</v>
       </c>
-      <c r="F9" s="3">
-        <f t="shared" si="1"/>
-        <v>132875.10574085417</v>
-      </c>
-      <c r="G9" s="8">
+      <c r="G9" s="3">
         <f t="shared" si="2"/>
-        <v>8.0077316241610745</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+        <v>132.87510574085417</v>
+      </c>
+      <c r="H9" s="17">
+        <f t="shared" si="3"/>
+        <v>8007.7316241610743</v>
+      </c>
+      <c r="I9" s="15">
+        <f t="shared" si="4"/>
+        <v>11.072925478404514</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
@@ -3668,22 +4125,30 @@
         <v>7421</v>
       </c>
       <c r="D10" s="3">
+        <f t="shared" si="1"/>
+        <v>60.827868852459019</v>
+      </c>
+      <c r="E10" s="3">
         <v>3819024349</v>
       </c>
-      <c r="E10" s="7">
+      <c r="F10" s="7">
         <f t="shared" si="0"/>
         <v>3819.0243489999998</v>
       </c>
-      <c r="F10" s="3">
-        <f t="shared" si="1"/>
-        <v>514623.95216278132</v>
-      </c>
-      <c r="G10" s="8">
+      <c r="G10" s="3">
         <f t="shared" si="2"/>
-        <v>31.303478270491805</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>514.62395216278128</v>
+      </c>
+      <c r="H10" s="17">
+        <f t="shared" si="3"/>
+        <v>31303.478270491803</v>
+      </c>
+      <c r="I10" s="15">
+        <f t="shared" si="4"/>
+        <v>42.885329346898438</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
@@ -3694,22 +4159,30 @@
         <v>59382</v>
       </c>
       <c r="D11" s="3">
+        <f t="shared" si="1"/>
+        <v>118.05566600397614</v>
+      </c>
+      <c r="E11" s="3">
         <v>18978868223</v>
       </c>
-      <c r="E11" s="7">
+      <c r="F11" s="7">
         <f t="shared" si="0"/>
         <v>18978.868223000001</v>
       </c>
-      <c r="F11" s="3">
-        <f t="shared" si="1"/>
-        <v>319606.41647300532</v>
-      </c>
-      <c r="G11" s="8">
+      <c r="G11" s="3">
         <f t="shared" si="2"/>
-        <v>37.73134835586481</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+        <v>319.60641647300531</v>
+      </c>
+      <c r="H11" s="17">
+        <f t="shared" si="3"/>
+        <v>37731.348355864808</v>
+      </c>
+      <c r="I11" s="15">
+        <f t="shared" si="4"/>
+        <v>26.633868039417109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
@@ -3720,22 +4193,30 @@
         <v>31240</v>
       </c>
       <c r="D12" s="3">
+        <f t="shared" si="1"/>
+        <v>182.69005847953215</v>
+      </c>
+      <c r="E12" s="3">
         <v>7362333654</v>
       </c>
-      <c r="E12" s="7">
+      <c r="F12" s="7">
         <f t="shared" si="0"/>
         <v>7362.333654</v>
       </c>
-      <c r="F12" s="3">
-        <f t="shared" si="1"/>
-        <v>235670.09135723431</v>
-      </c>
-      <c r="G12" s="8">
+      <c r="G12" s="3">
         <f t="shared" si="2"/>
-        <v>43.054582771929823</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>235.67009135723433</v>
+      </c>
+      <c r="H12" s="17">
+        <f t="shared" si="3"/>
+        <v>43054.582771929825</v>
+      </c>
+      <c r="I12" s="15">
+        <f t="shared" si="4"/>
+        <v>19.639174279769527</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
@@ -3746,22 +4227,30 @@
         <v>62974</v>
       </c>
       <c r="D13" s="3">
+        <f t="shared" si="1"/>
+        <v>111.85435168738898</v>
+      </c>
+      <c r="E13" s="3">
         <v>7989186541</v>
       </c>
-      <c r="E13" s="7">
+      <c r="F13" s="7">
         <f t="shared" si="0"/>
         <v>7989.186541</v>
       </c>
-      <c r="F13" s="3">
-        <f t="shared" si="1"/>
-        <v>126864.84169657319</v>
-      </c>
-      <c r="G13" s="8">
+      <c r="G13" s="3">
         <f t="shared" si="2"/>
-        <v>14.190384619893427</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>126.86484169657319</v>
+      </c>
+      <c r="H13" s="17">
+        <f t="shared" si="3"/>
+        <v>14190.384619893428</v>
+      </c>
+      <c r="I13" s="15">
+        <f t="shared" si="4"/>
+        <v>10.572070141381099</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>19</v>
       </c>
@@ -3772,22 +4261,30 @@
         <v>39314</v>
       </c>
       <c r="D14" s="3">
+        <f t="shared" si="1"/>
+        <v>89.757990867579906</v>
+      </c>
+      <c r="E14" s="3">
         <v>9372191123</v>
       </c>
-      <c r="E14" s="7">
+      <c r="F14" s="7">
         <f t="shared" si="0"/>
         <v>9372.1911230000005</v>
       </c>
-      <c r="F14" s="3">
-        <f t="shared" si="1"/>
-        <v>238393.22182937377</v>
-      </c>
-      <c r="G14" s="8">
+      <c r="G14" s="3">
         <f t="shared" si="2"/>
-        <v>21.397696627853882</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>238.39322182937374</v>
+      </c>
+      <c r="H14" s="17">
+        <f t="shared" si="3"/>
+        <v>21397.696627853882</v>
+      </c>
+      <c r="I14" s="15">
+        <f t="shared" si="4"/>
+        <v>19.86610181911448</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
@@ -3798,22 +4295,30 @@
         <v>13174</v>
       </c>
       <c r="D15" s="3">
+        <f t="shared" si="1"/>
+        <v>105.392</v>
+      </c>
+      <c r="E15" s="3">
         <v>3706062574</v>
       </c>
-      <c r="E15" s="7">
+      <c r="F15" s="7">
         <f t="shared" si="0"/>
         <v>3706.062574</v>
       </c>
-      <c r="F15" s="3">
-        <f t="shared" si="1"/>
-        <v>281316.42432063154</v>
-      </c>
-      <c r="G15" s="8">
+      <c r="G15" s="3">
         <f t="shared" si="2"/>
-        <v>29.648500592000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+        <v>281.31642432063154</v>
+      </c>
+      <c r="H15" s="17">
+        <f t="shared" si="3"/>
+        <v>29648.500592</v>
+      </c>
+      <c r="I15" s="15">
+        <f t="shared" si="4"/>
+        <v>23.44303536005263</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
@@ -3824,22 +4329,30 @@
         <v>34647</v>
       </c>
       <c r="D16" s="3">
+        <f t="shared" si="1"/>
+        <v>79.831797235023046</v>
+      </c>
+      <c r="E16" s="3">
         <v>4039069361</v>
       </c>
-      <c r="E16" s="7">
+      <c r="F16" s="7">
         <f t="shared" si="0"/>
         <v>4039.0693609999998</v>
       </c>
-      <c r="F16" s="3">
-        <f t="shared" si="1"/>
-        <v>116577.75163794846</v>
-      </c>
-      <c r="G16" s="8">
+      <c r="G16" s="3">
         <f t="shared" si="2"/>
-        <v>9.3066114308755754</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>116.57775163794845</v>
+      </c>
+      <c r="H16" s="17">
+        <f t="shared" si="3"/>
+        <v>9306.611430875575</v>
+      </c>
+      <c r="I16" s="15">
+        <f t="shared" si="4"/>
+        <v>9.7148126364957044</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>22</v>
       </c>
@@ -3850,22 +4363,30 @@
         <v>23580</v>
       </c>
       <c r="D17" s="3">
+        <f t="shared" si="1"/>
+        <v>166.05633802816902</v>
+      </c>
+      <c r="E17" s="3">
         <v>4164940526</v>
       </c>
-      <c r="E17" s="7">
+      <c r="F17" s="7">
         <f t="shared" si="0"/>
         <v>4164.9405260000003</v>
       </c>
-      <c r="F17" s="3">
-        <f t="shared" si="1"/>
-        <v>176630.21738761663</v>
-      </c>
-      <c r="G17" s="8">
+      <c r="G17" s="3">
         <f t="shared" si="2"/>
-        <v>29.330567084507042</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>176.63021738761663</v>
+      </c>
+      <c r="H17" s="17">
+        <f t="shared" si="3"/>
+        <v>29330.567084507042</v>
+      </c>
+      <c r="I17" s="15">
+        <f t="shared" si="4"/>
+        <v>14.719184782301385</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>23</v>
       </c>
@@ -3876,22 +4397,30 @@
         <v>16841</v>
       </c>
       <c r="D18" s="3">
+        <f t="shared" si="1"/>
+        <v>61.24</v>
+      </c>
+      <c r="E18" s="3">
         <v>1673660110</v>
       </c>
-      <c r="E18" s="7">
+      <c r="F18" s="7">
         <f t="shared" si="0"/>
         <v>1673.66011</v>
       </c>
-      <c r="F18" s="3">
-        <f t="shared" si="1"/>
-        <v>99380.090849712011</v>
-      </c>
-      <c r="G18" s="8">
+      <c r="G18" s="3">
         <f t="shared" si="2"/>
-        <v>6.0860367636363639</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+        <v>99.380090849712019</v>
+      </c>
+      <c r="H18" s="17">
+        <f t="shared" si="3"/>
+        <v>6086.0367636363635</v>
+      </c>
+      <c r="I18" s="15">
+        <f t="shared" si="4"/>
+        <v>8.2816742374760022</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>24</v>
       </c>
@@ -3902,22 +4431,30 @@
         <v>10463</v>
       </c>
       <c r="D19" s="3">
+        <f t="shared" si="1"/>
+        <v>93.419642857142861</v>
+      </c>
+      <c r="E19" s="3">
         <v>778514487</v>
       </c>
-      <c r="E19" s="7">
+      <c r="F19" s="7">
         <f t="shared" si="0"/>
         <v>778.51448700000003</v>
       </c>
-      <c r="F19" s="3">
-        <f t="shared" si="1"/>
-        <v>74406.430947147092</v>
-      </c>
-      <c r="G19" s="8">
+      <c r="G19" s="3">
         <f t="shared" si="2"/>
-        <v>6.9510222053571429</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>74.406430947147086</v>
+      </c>
+      <c r="H19" s="17">
+        <f t="shared" si="3"/>
+        <v>6951.0222053571424</v>
+      </c>
+      <c r="I19" s="15">
+        <f t="shared" si="4"/>
+        <v>6.2005359122622572</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>25</v>
       </c>
@@ -3928,22 +4465,30 @@
         <v>6880</v>
       </c>
       <c r="D20" s="3">
+        <f t="shared" si="1"/>
+        <v>215</v>
+      </c>
+      <c r="E20" s="3">
         <v>1226916083</v>
       </c>
-      <c r="E20" s="7">
+      <c r="F20" s="7">
         <f t="shared" si="0"/>
         <v>1226.9160830000001</v>
       </c>
-      <c r="F20" s="3">
-        <f t="shared" si="1"/>
-        <v>178330.82601744187</v>
-      </c>
-      <c r="G20" s="8">
+      <c r="G20" s="3">
         <f t="shared" si="2"/>
-        <v>38.341127593750002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>178.33082601744186</v>
+      </c>
+      <c r="H20" s="17">
+        <f t="shared" si="3"/>
+        <v>38341.127593750003</v>
+      </c>
+      <c r="I20" s="15">
+        <f t="shared" si="4"/>
+        <v>14.860902168120155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>26</v>
       </c>
@@ -3954,22 +4499,30 @@
         <v>17096</v>
       </c>
       <c r="D21" s="3">
+        <f t="shared" si="1"/>
+        <v>75.312775330396477</v>
+      </c>
+      <c r="E21" s="3">
         <v>1596628479</v>
       </c>
-      <c r="E21" s="7">
+      <c r="F21" s="7">
         <f t="shared" si="0"/>
         <v>1596.628479</v>
       </c>
-      <c r="F21" s="3">
-        <f t="shared" si="1"/>
-        <v>93391.932557323351</v>
-      </c>
-      <c r="G21" s="8">
+      <c r="G21" s="3">
         <f t="shared" si="2"/>
-        <v>7.0336056343612334</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>93.391932557323358</v>
+      </c>
+      <c r="H21" s="17">
+        <f t="shared" si="3"/>
+        <v>7033.6056343612336</v>
+      </c>
+      <c r="I21" s="15">
+        <f t="shared" si="4"/>
+        <v>7.7826610464436135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>27</v>
       </c>
@@ -3980,19 +4533,55 @@
         <v>59219</v>
       </c>
       <c r="D22" s="3">
+        <f t="shared" si="1"/>
+        <v>98.044701986754973</v>
+      </c>
+      <c r="E22" s="3">
         <v>16290782103</v>
       </c>
-      <c r="E22" s="7">
+      <c r="F22" s="7">
         <f t="shared" si="0"/>
         <v>16290.782103</v>
       </c>
-      <c r="F22" s="3">
-        <f t="shared" si="1"/>
-        <v>275093.83986558369</v>
-      </c>
-      <c r="G22" s="8">
+      <c r="G22" s="3">
         <f t="shared" si="2"/>
-        <v>26.971493548013243</v>
+        <v>275.09383986558367</v>
+      </c>
+      <c r="H22" s="17">
+        <f t="shared" si="3"/>
+        <v>26971.493548013244</v>
+      </c>
+      <c r="I22" s="15">
+        <f t="shared" si="4"/>
+        <v>22.924486655465305</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B23" s="12">
+        <f>SUM(B2:B22)</f>
+        <v>6583</v>
+      </c>
+      <c r="C23" s="12">
+        <f>SUM(C2:C22)</f>
+        <v>730236</v>
+      </c>
+      <c r="E23" s="12">
+        <f>SUM(E2:E22)</f>
+        <v>148266441739</v>
+      </c>
+      <c r="I23" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="15">
+        <f>C23/B23</f>
+        <v>110.92754063496886</v>
+      </c>
+      <c r="I24" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4013,16 +4602,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>29</v>
@@ -4031,1806 +4620,1806 @@
         <v>30</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <v>41513051405</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="9">
         <v>1287</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="9">
         <v>32255673.197358198</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <v>184924</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="9">
         <v>122748</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="9">
         <v>62176</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="9">
         <v>0.66377538880837528</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="9">
         <v>0.33622461119162472</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="9">
         <v>24822</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="9">
         <v>0.13422811533386689</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="9">
         <v>168</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="9">
         <v>9.084813220566287E-4</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="9">
         <v>109757</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="9">
         <v>0.59352490752957976</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="9">
         <v>50177</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="9">
         <v>0.27133849581449682</v>
       </c>
-      <c r="R2" s="10">
+      <c r="R2" s="9">
         <v>224487.094184638</v>
       </c>
-      <c r="S2" s="10">
+      <c r="S2" s="9">
         <v>58256.121328531422</v>
       </c>
-      <c r="T2" s="10">
+      <c r="T2" s="9">
         <v>38995.364896999738</v>
       </c>
-      <c r="U2" s="10">
+      <c r="U2" s="9">
         <v>69638.500906789966</v>
       </c>
-      <c r="V2" s="10">
+      <c r="V2" s="9">
         <v>49912.860391295893</v>
       </c>
-      <c r="W2" s="10">
+      <c r="W2" s="9">
         <v>292756.70455157763</v>
       </c>
-      <c r="X2" s="10">
+      <c r="X2" s="9">
         <v>7472600317952</v>
       </c>
-      <c r="Y2" s="10">
+      <c r="Y2" s="9">
         <v>25524950</v>
       </c>
-      <c r="Z2" s="10">
+      <c r="Z2" s="9">
         <v>16800000</v>
       </c>
-      <c r="AA2" s="10">
+      <c r="AA2" s="9">
         <v>2127079.166666667</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="9">
         <v>7916248241</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <v>53</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <v>149363174.35849059</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <v>12577</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <v>9456</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <v>3121</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="9">
         <v>0.7518486125467122</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="9">
         <v>0.24815138745328769</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="9">
         <v>1385</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="9">
         <v>0.1101216506321062</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="9">
         <v>11</v>
       </c>
-      <c r="M3" s="10">
+      <c r="M3" s="9">
         <v>8.7461238769181841E-4</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="9">
         <v>4416</v>
       </c>
-      <c r="O3" s="10">
+      <c r="O3" s="9">
         <v>0.35111711854973371</v>
       </c>
-      <c r="P3" s="10">
+      <c r="P3" s="9">
         <v>6765</v>
       </c>
-      <c r="Q3" s="10">
+      <c r="Q3" s="9">
         <v>0.53788661843046837</v>
       </c>
-      <c r="R3" s="10">
+      <c r="R3" s="9">
         <v>629422.61596565158</v>
       </c>
-      <c r="S3" s="10">
+      <c r="S3" s="9">
         <v>114584.5078796562</v>
       </c>
-      <c r="T3" s="10">
+      <c r="T3" s="9">
         <v>60024.80865036232</v>
       </c>
-      <c r="U3" s="10">
+      <c r="U3" s="9">
         <v>78295.286326681453</v>
       </c>
-      <c r="V3" s="10">
+      <c r="V3" s="9">
         <v>75908.176830722747</v>
       </c>
-      <c r="W3" s="10">
+      <c r="W3" s="9">
         <v>53982.389692664146</v>
       </c>
-      <c r="X3" s="10">
+      <c r="X3" s="9">
         <v>1589056897024</v>
       </c>
-      <c r="Y3" s="10">
+      <c r="Y3" s="9">
         <v>29436578</v>
       </c>
-      <c r="Z3" s="10">
+      <c r="Z3" s="9">
         <v>18000000</v>
       </c>
-      <c r="AA3" s="10">
+      <c r="AA3" s="9">
         <v>2453048.166666667</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <v>2657337121</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="9">
         <v>199</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <v>13353452.86934673</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="9">
         <v>27878</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <v>17939</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <v>9939</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="9">
         <v>0.64348231580457704</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="9">
         <v>0.3565176841954229</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="9">
         <v>3459</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="9">
         <v>0.124076332592008</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="9">
         <v>13</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="9">
         <v>4.6631752636487552E-4</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="9">
         <v>18613</v>
       </c>
-      <c r="O4" s="10">
+      <c r="O4" s="9">
         <v>0.66765908601764834</v>
       </c>
-      <c r="P4" s="10">
+      <c r="P4" s="9">
         <v>5793</v>
       </c>
-      <c r="Q4" s="10">
+      <c r="Q4" s="9">
         <v>0.20779826386397879</v>
       </c>
-      <c r="R4" s="10">
+      <c r="R4" s="9">
         <v>95320.220998636913</v>
       </c>
-      <c r="S4" s="10">
+      <c r="S4" s="9">
         <v>58933.520737327191</v>
       </c>
-      <c r="T4" s="10">
+      <c r="T4" s="9">
         <v>32534.454682211359</v>
       </c>
-      <c r="U4" s="10">
+      <c r="U4" s="9">
         <v>77586.766787502158</v>
       </c>
-      <c r="V4" s="10">
+      <c r="V4" s="9">
         <v>45184.056675514737</v>
       </c>
-      <c r="W4" s="10">
+      <c r="W4" s="9">
         <v>33381.501019895077</v>
       </c>
-      <c r="X4" s="10">
+      <c r="X4" s="9">
         <v>801464188928</v>
       </c>
-      <c r="Y4" s="10">
+      <c r="Y4" s="9">
         <v>24009232</v>
       </c>
-      <c r="Z4" s="10">
+      <c r="Z4" s="9">
         <v>16800000</v>
       </c>
-      <c r="AA4" s="10">
+      <c r="AA4" s="9">
         <v>2000769.333333333</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="9">
         <v>5608420074</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="9">
         <v>605</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <v>9270115.8247933891</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="9">
         <v>66014</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="9">
         <v>20680</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="9">
         <v>45334</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="9">
         <v>0.31326688278244008</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="9">
         <v>0.68673311721755992</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="9">
         <v>6705</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="9">
         <v>0.10156936407428729</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="9">
         <v>112</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="9">
         <v>1.696609810040295E-3</v>
       </c>
-      <c r="N5" s="10">
+      <c r="N5" s="9">
         <v>43090</v>
       </c>
-      <c r="O5" s="10">
+      <c r="O5" s="9">
         <v>0.65274032780925262</v>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="9">
         <v>16107</v>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="9">
         <v>0.24399369830641979</v>
       </c>
-      <c r="R5" s="10">
+      <c r="R5" s="9">
         <v>84958.040324779591</v>
       </c>
-      <c r="S5" s="10">
+      <c r="S5" s="9">
         <v>49994.283849200518</v>
       </c>
-      <c r="T5" s="10">
+      <c r="T5" s="9">
         <v>28625.878602924109</v>
       </c>
-      <c r="U5" s="10">
+      <c r="U5" s="9">
         <v>59164.37275718632</v>
       </c>
-      <c r="V5" s="10">
+      <c r="V5" s="9">
         <v>38283.707910443241</v>
       </c>
-      <c r="W5" s="10">
+      <c r="W5" s="9">
         <v>156115.59936070439</v>
       </c>
-      <c r="X5" s="10">
+      <c r="X5" s="9">
         <v>3258957692928</v>
       </c>
-      <c r="Y5" s="10">
+      <c r="Y5" s="9">
         <v>20875286</v>
       </c>
-      <c r="Z5" s="10">
+      <c r="Z5" s="9">
         <v>15600000</v>
       </c>
-      <c r="AA5" s="10">
+      <c r="AA5" s="9">
         <v>1739607.166666667</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="9">
         <v>856536941</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <v>174</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>4922626.0977011491</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <v>14298</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <v>7301</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <v>6997</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <v>0.51063085746258219</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="9">
         <v>0.48936914253741781</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="9">
         <v>1142</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="9">
         <v>7.9871310672821369E-2</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="9">
         <v>21</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="9">
         <v>1.4687368862778009E-3</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="9">
         <v>9801</v>
       </c>
-      <c r="O6" s="10">
+      <c r="O6" s="9">
         <v>0.68548048678136797</v>
       </c>
-      <c r="P6" s="10">
+      <c r="P6" s="9">
         <v>3334</v>
       </c>
-      <c r="Q6" s="10">
+      <c r="Q6" s="9">
         <v>0.23317946565953279</v>
       </c>
-      <c r="R6" s="10">
+      <c r="R6" s="9">
         <v>59906.066652678703</v>
       </c>
-      <c r="S6" s="10">
+      <c r="S6" s="9">
         <v>59824.983662940671</v>
       </c>
-      <c r="T6" s="10">
+      <c r="T6" s="9">
         <v>27406.555555555551</v>
       </c>
-      <c r="U6" s="10">
+      <c r="U6" s="9">
         <v>63385.710857828431</v>
       </c>
-      <c r="V6" s="10">
+      <c r="V6" s="9">
         <v>38433.070988949497</v>
       </c>
-      <c r="W6" s="10">
+      <c r="W6" s="9">
         <v>40735.455275535583</v>
       </c>
-      <c r="X6" s="10">
+      <c r="X6" s="9">
         <v>739507306496</v>
       </c>
-      <c r="Y6" s="10">
+      <c r="Y6" s="9">
         <v>18153898</v>
       </c>
-      <c r="Z6" s="10">
+      <c r="Z6" s="9">
         <v>15600000</v>
       </c>
-      <c r="AA6" s="10">
+      <c r="AA6" s="9">
         <v>1512824.833333333</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="9">
         <v>364104823</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <v>89</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>4091065.4269662919</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="9">
         <v>3708</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="9">
         <v>3013</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="9">
         <v>695</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="9">
         <v>0.81256742179072272</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="9">
         <v>0.18743257820927731</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="9">
         <v>305</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="9">
         <v>8.2254584681769147E-2</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="9">
         <v>4</v>
       </c>
-      <c r="M7" s="10">
+      <c r="M7" s="9">
         <v>1.078748651564185E-3</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N7" s="9">
         <v>2621</v>
       </c>
-      <c r="O7" s="10">
+      <c r="O7" s="9">
         <v>0.70685005393743261</v>
       </c>
-      <c r="P7" s="10">
+      <c r="P7" s="9">
         <v>778</v>
       </c>
-      <c r="Q7" s="10">
+      <c r="Q7" s="9">
         <v>0.2098166127292341</v>
       </c>
-      <c r="R7" s="10">
+      <c r="R7" s="9">
         <v>98194.396709816618</v>
       </c>
-      <c r="S7" s="10">
+      <c r="S7" s="9">
         <v>81996.336569579289</v>
       </c>
-      <c r="T7" s="10">
+      <c r="T7" s="9">
         <v>30320.499046165591</v>
       </c>
-      <c r="U7" s="10">
+      <c r="U7" s="9">
         <v>64857.182519280213</v>
       </c>
-      <c r="V7" s="10">
+      <c r="V7" s="9">
         <v>41873.188781014032</v>
       </c>
-      <c r="W7" s="10">
+      <c r="W7" s="9">
         <v>7992.1848473548889</v>
       </c>
-      <c r="X7" s="10">
+      <c r="X7" s="9">
         <v>179486179328</v>
       </c>
-      <c r="Y7" s="10">
+      <c r="Y7" s="9">
         <v>22457712</v>
       </c>
-      <c r="Z7" s="10">
+      <c r="Z7" s="9">
         <v>15600000</v>
       </c>
-      <c r="AA7" s="10">
+      <c r="AA7" s="9">
         <v>1871476</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <v>5966261497</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <v>130</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>45894319.20769231</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="9">
         <v>20647</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="9">
         <v>14772</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="9">
         <v>5875</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="9">
         <v>0.71545502978640962</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="9">
         <v>0.28454497021359038</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="9">
         <v>3650</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="9">
         <v>0.176781130430571</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="9">
         <v>12</v>
       </c>
-      <c r="M8" s="10">
+      <c r="M8" s="9">
         <v>5.8119823703201435E-4</v>
       </c>
-      <c r="N8" s="10">
+      <c r="N8" s="9">
         <v>12137</v>
       </c>
-      <c r="O8" s="10">
+      <c r="O8" s="9">
         <v>0.5878335835714632</v>
       </c>
-      <c r="P8" s="10">
+      <c r="P8" s="9">
         <v>4848</v>
       </c>
-      <c r="Q8" s="10">
+      <c r="Q8" s="9">
         <v>0.23480408776093381</v>
       </c>
-      <c r="R8" s="10">
+      <c r="R8" s="9">
         <v>288965.05531069892</v>
       </c>
-      <c r="S8" s="10">
+      <c r="S8" s="9">
         <v>121858.6127799017</v>
       </c>
-      <c r="T8" s="10">
+      <c r="T8" s="9">
         <v>48587.34571970009</v>
       </c>
-      <c r="U8" s="10">
+      <c r="U8" s="9">
         <v>111106.88448844881</v>
       </c>
-      <c r="V8" s="10">
+      <c r="V8" s="9">
         <v>76262.751247154549</v>
       </c>
-      <c r="W8" s="10">
+      <c r="W8" s="9">
         <v>36072.072888374329</v>
       </c>
-      <c r="X8" s="10">
+      <c r="X8" s="9">
         <v>1498787872768</v>
       </c>
-      <c r="Y8" s="10">
+      <c r="Y8" s="9">
         <v>41549812</v>
       </c>
-      <c r="Z8" s="10">
+      <c r="Z8" s="9">
         <v>18000000</v>
       </c>
-      <c r="AA8" s="10">
+      <c r="AA8" s="9">
         <v>3462484.333333333</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="9">
         <v>2386304024</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <v>298</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>8007731.6241610739</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="9">
         <v>17959</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <v>10433</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="9">
         <v>7526</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="9">
         <v>0.5809343504649479</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="9">
         <v>0.41906564953505199</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="9">
         <v>2695</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="9">
         <v>0.1500640347458099</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="9">
         <v>20</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9" s="9">
         <v>1.113647753215658E-3</v>
       </c>
-      <c r="N9" s="10">
+      <c r="N9" s="9">
         <v>10896</v>
       </c>
-      <c r="O9" s="10">
+      <c r="O9" s="9">
         <v>0.60671529595189044</v>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="9">
         <v>4348</v>
       </c>
-      <c r="Q9" s="10">
+      <c r="Q9" s="9">
         <v>0.24210702154908401</v>
       </c>
-      <c r="R9" s="10">
+      <c r="R9" s="9">
         <v>132875.1057408542</v>
       </c>
-      <c r="S9" s="10">
+      <c r="S9" s="9">
         <v>54490.335911602211</v>
       </c>
-      <c r="T9" s="10">
+      <c r="T9" s="9">
         <v>34344.688050660792</v>
       </c>
-      <c r="U9" s="10">
+      <c r="U9" s="9">
         <v>70162.488500459978</v>
       </c>
-      <c r="V9" s="10">
+      <c r="V9" s="9">
         <v>46062.00139205969</v>
       </c>
-      <c r="W9" s="10">
+      <c r="W9" s="9">
         <v>14227.397269248961</v>
       </c>
-      <c r="X9" s="10">
+      <c r="X9" s="9">
         <v>320827621376</v>
       </c>
-      <c r="Y9" s="10">
+      <c r="Y9" s="9">
         <v>22549986</v>
       </c>
-      <c r="Z9" s="10">
+      <c r="Z9" s="9">
         <v>18000000</v>
       </c>
-      <c r="AA9" s="10">
+      <c r="AA9" s="9">
         <v>1879165.5</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <v>3819024349</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <v>122</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <v>31303478.270491801</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="9">
         <v>7421</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <v>5679</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="9">
         <v>1742</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="9">
         <v>0.76526074653011722</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="9">
         <v>0.23473925346988281</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="9">
         <v>2328</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="9">
         <v>0.31370435251313838</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="9">
         <v>3</v>
       </c>
-      <c r="M10" s="10">
+      <c r="M10" s="9">
         <v>4.0425818622827109E-4</v>
       </c>
-      <c r="N10" s="10">
+      <c r="N10" s="9">
         <v>3442</v>
       </c>
-      <c r="O10" s="10">
+      <c r="O10" s="9">
         <v>0.46381889233256968</v>
       </c>
-      <c r="P10" s="10">
+      <c r="P10" s="9">
         <v>1648</v>
       </c>
-      <c r="Q10" s="10">
+      <c r="Q10" s="9">
         <v>0.22207249696806361</v>
       </c>
-      <c r="R10" s="10">
+      <c r="R10" s="9">
         <v>514623.95216278132</v>
       </c>
-      <c r="S10" s="10">
+      <c r="S10" s="9">
         <v>154190.2621192621</v>
       </c>
-      <c r="T10" s="10">
+      <c r="T10" s="9">
         <v>62280.843695525858</v>
       </c>
-      <c r="U10" s="10">
+      <c r="U10" s="9">
         <v>106340.96359223301</v>
       </c>
-      <c r="V10" s="10">
+      <c r="V10" s="9">
         <v>100934.9242689665</v>
       </c>
-      <c r="W10" s="10">
+      <c r="W10" s="9">
         <v>7219.251886844635</v>
       </c>
-      <c r="X10" s="10">
+      <c r="X10" s="9">
         <v>217988431872</v>
       </c>
-      <c r="Y10" s="10">
+      <c r="Y10" s="9">
         <v>30195434</v>
       </c>
-      <c r="Z10" s="10">
+      <c r="Z10" s="9">
         <v>18000000</v>
       </c>
-      <c r="AA10" s="10">
+      <c r="AA10" s="9">
         <v>2516286.166666667</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>18978868223</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="9">
         <v>503</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>37731348.355864808</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="9">
         <v>59382</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="9">
         <v>34674</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="9">
         <v>24708</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="9">
         <v>0.58391431746994038</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="9">
         <v>0.41608568253005962</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="9">
         <v>9544</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="9">
         <v>0.1607221043413829</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="9">
         <v>79</v>
       </c>
-      <c r="M11" s="10">
+      <c r="M11" s="9">
         <v>1.330369472230642E-3</v>
       </c>
-      <c r="N11" s="10">
+      <c r="N11" s="9">
         <v>28728</v>
       </c>
-      <c r="O11" s="10">
+      <c r="O11" s="9">
         <v>0.48378296453470748</v>
       </c>
-      <c r="P11" s="10">
+      <c r="P11" s="9">
         <v>21031</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="Q11" s="9">
         <v>0.35416456165167898</v>
       </c>
-      <c r="R11" s="10">
+      <c r="R11" s="9">
         <v>319606.41647300532</v>
       </c>
-      <c r="S11" s="10">
+      <c r="S11" s="9">
         <v>81042.841317676401</v>
       </c>
-      <c r="T11" s="10">
+      <c r="T11" s="9">
         <v>42697.25</v>
       </c>
-      <c r="U11" s="10">
+      <c r="U11" s="9">
         <v>91051.250011887212</v>
       </c>
-      <c r="V11" s="10">
+      <c r="V11" s="9">
         <v>66036.521454312751</v>
       </c>
-      <c r="W11" s="10">
+      <c r="W11" s="9">
         <v>81296.940004348755</v>
       </c>
-      <c r="X11" s="10">
+      <c r="X11" s="9">
         <v>2292983267328</v>
       </c>
-      <c r="Y11" s="10">
+      <c r="Y11" s="9">
         <v>28205038</v>
       </c>
-      <c r="Z11" s="10">
+      <c r="Z11" s="9">
         <v>18000000</v>
       </c>
-      <c r="AA11" s="10">
+      <c r="AA11" s="9">
         <v>2350419.833333333</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <v>7362333654</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="9">
         <v>171</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <v>43054582.771929823</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="9">
         <v>31240</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="9">
         <v>14196</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="9">
         <v>17044</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="9">
         <v>0.45441741357234322</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="9">
         <v>0.54558258642765689</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="9">
         <v>7456</v>
       </c>
-      <c r="K12" s="10">
+      <c r="K12" s="9">
         <v>0.23866837387964149</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L12" s="9">
         <v>36</v>
       </c>
-      <c r="M12" s="10">
+      <c r="M12" s="9">
         <v>1.1523687580025611E-3</v>
       </c>
-      <c r="N12" s="10">
+      <c r="N12" s="9">
         <v>13612</v>
       </c>
-      <c r="O12" s="10">
+      <c r="O12" s="9">
         <v>0.43572343149807941</v>
       </c>
-      <c r="P12" s="10">
+      <c r="P12" s="9">
         <v>10136</v>
       </c>
-      <c r="Q12" s="10">
+      <c r="Q12" s="9">
         <v>0.32445582586427663</v>
       </c>
-      <c r="R12" s="10">
+      <c r="R12" s="9">
         <v>235670.09135723431</v>
       </c>
-      <c r="S12" s="10">
+      <c r="S12" s="9">
         <v>76360.745595301662</v>
       </c>
-      <c r="T12" s="10">
+      <c r="T12" s="9">
         <v>42392.343961210703</v>
       </c>
-      <c r="U12" s="10">
+      <c r="U12" s="9">
         <v>102431.9328137332</v>
       </c>
-      <c r="V12" s="10">
+      <c r="V12" s="9">
         <v>70018.865941101147</v>
       </c>
-      <c r="W12" s="10">
+      <c r="W12" s="9">
         <v>50389.893980741501</v>
       </c>
-      <c r="X12" s="10">
+      <c r="X12" s="9">
         <v>2090827382784</v>
       </c>
-      <c r="Y12" s="10">
+      <c r="Y12" s="9">
         <v>41492988</v>
       </c>
-      <c r="Z12" s="10">
+      <c r="Z12" s="9">
         <v>22584000</v>
       </c>
-      <c r="AA12" s="10">
+      <c r="AA12" s="9">
         <v>3457749</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <v>7989186541</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="9">
         <v>563</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>14190384.61989343</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="9">
         <v>62974</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="9">
         <v>40513</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="9">
         <v>22461</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="9">
         <v>0.64332899291771206</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="9">
         <v>0.35667100708228788</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="9">
         <v>9648</v>
       </c>
-      <c r="K13" s="10">
+      <c r="K13" s="9">
         <v>0.15320608505097341</v>
       </c>
-      <c r="L13" s="10">
+      <c r="L13" s="9">
         <v>59</v>
       </c>
-      <c r="M13" s="10">
+      <c r="M13" s="9">
         <v>9.368945914186807E-4</v>
       </c>
-      <c r="N13" s="10">
+      <c r="N13" s="9">
         <v>39197</v>
       </c>
-      <c r="O13" s="10">
+      <c r="O13" s="9">
         <v>0.62243147965827161</v>
       </c>
-      <c r="P13" s="10">
+      <c r="P13" s="9">
         <v>14070</v>
       </c>
-      <c r="Q13" s="10">
+      <c r="Q13" s="9">
         <v>0.22342554069933621</v>
       </c>
-      <c r="R13" s="10">
+      <c r="R13" s="9">
         <v>126864.8416965732</v>
       </c>
-      <c r="S13" s="10">
+      <c r="S13" s="9">
         <v>60291.353456268669</v>
       </c>
-      <c r="T13" s="10">
+      <c r="T13" s="9">
         <v>35967.423042579787</v>
       </c>
-      <c r="U13" s="10">
+      <c r="U13" s="9">
         <v>79032.197867803843</v>
       </c>
-      <c r="V13" s="10">
+      <c r="V13" s="9">
         <v>49338.556753580837</v>
       </c>
-      <c r="W13" s="10">
+      <c r="W13" s="9">
         <v>95304.083910703659</v>
       </c>
-      <c r="X13" s="10">
+      <c r="X13" s="9">
         <v>2442556342272</v>
       </c>
-      <c r="Y13" s="10">
+      <c r="Y13" s="9">
         <v>25629082</v>
       </c>
-      <c r="Z13" s="10">
+      <c r="Z13" s="9">
         <v>17544000</v>
       </c>
-      <c r="AA13" s="10">
+      <c r="AA13" s="9">
         <v>2135756.833333333</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <v>9372191123</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <v>438</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <v>21397696.627853882</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>39314</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="9">
         <v>34000</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="9">
         <v>5314</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="9">
         <v>0.8648318665106578</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="9">
         <v>0.1351681334893422</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="9">
         <v>4596</v>
       </c>
-      <c r="K14" s="10">
+      <c r="K14" s="9">
         <v>0.1169049193671466</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="9">
         <v>19</v>
       </c>
-      <c r="M14" s="10">
+      <c r="M14" s="9">
         <v>4.8328839599124989E-4</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="9">
         <v>27701</v>
       </c>
-      <c r="O14" s="10">
+      <c r="O14" s="9">
         <v>0.70460904512387446</v>
       </c>
-      <c r="P14" s="10">
+      <c r="P14" s="9">
         <v>6998</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="Q14" s="9">
         <v>0.17800274711298769</v>
       </c>
-      <c r="R14" s="10">
+      <c r="R14" s="9">
         <v>238393.2218293738</v>
       </c>
-      <c r="S14" s="10">
+      <c r="S14" s="9">
         <v>80409.660021668475</v>
       </c>
-      <c r="T14" s="10">
+      <c r="T14" s="9">
         <v>47340.585213530198</v>
       </c>
-      <c r="U14" s="10">
+      <c r="U14" s="9">
         <v>82590.511003143751</v>
       </c>
-      <c r="V14" s="10">
+      <c r="V14" s="9">
         <v>57497.088340031543</v>
       </c>
-      <c r="W14" s="10">
+      <c r="W14" s="9">
         <v>65302.21913433075</v>
       </c>
-      <c r="X14" s="10">
+      <c r="X14" s="9">
         <v>2141214474240</v>
       </c>
-      <c r="Y14" s="10">
+      <c r="Y14" s="9">
         <v>32789306</v>
       </c>
-      <c r="Z14" s="10">
+      <c r="Z14" s="9">
         <v>18000000</v>
       </c>
-      <c r="AA14" s="10">
+      <c r="AA14" s="9">
         <v>2732442.166666667</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <v>3706062574</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="9">
         <v>125</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <v>29648500.592</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="9">
         <v>13174</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="9">
         <v>11104</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="9">
         <v>2070</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="9">
         <v>0.84287232427508729</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="9">
         <v>0.15712767572491271</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J15" s="9">
         <v>2188</v>
       </c>
-      <c r="K15" s="10">
+      <c r="K15" s="9">
         <v>0.16608471231213001</v>
       </c>
-      <c r="L15" s="10">
+      <c r="L15" s="9">
         <v>27</v>
       </c>
-      <c r="M15" s="10">
+      <c r="M15" s="9">
         <v>2.0494914224988611E-3</v>
       </c>
-      <c r="N15" s="10">
+      <c r="N15" s="9">
         <v>7750</v>
       </c>
-      <c r="O15" s="10">
+      <c r="O15" s="9">
         <v>0.58827994534689543</v>
       </c>
-      <c r="P15" s="10">
+      <c r="P15" s="9">
         <v>3209</v>
       </c>
-      <c r="Q15" s="10">
+      <c r="Q15" s="9">
         <v>0.24358585091847579</v>
       </c>
-      <c r="R15" s="10">
+      <c r="R15" s="9">
         <v>281316.42432063149</v>
       </c>
-      <c r="S15" s="10">
+      <c r="S15" s="9">
         <v>66543.927313769746</v>
       </c>
-      <c r="T15" s="10">
+      <c r="T15" s="9">
         <v>51463.606064516127</v>
       </c>
-      <c r="U15" s="10">
+      <c r="U15" s="9">
         <v>99677.63010283577</v>
       </c>
-      <c r="V15" s="10">
+      <c r="V15" s="9">
         <v>65743.378169121002</v>
       </c>
-      <c r="W15" s="10">
+      <c r="W15" s="9">
         <v>16507.17465925217</v>
       </c>
-      <c r="X15" s="10">
+      <c r="X15" s="9">
         <v>420233314304</v>
       </c>
-      <c r="Y15" s="10">
+      <c r="Y15" s="9">
         <v>25457616</v>
       </c>
-      <c r="Z15" s="10">
+      <c r="Z15" s="9">
         <v>20400000</v>
       </c>
-      <c r="AA15" s="10">
+      <c r="AA15" s="9">
         <v>2121468</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <v>4039069361</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <v>434</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <v>9306611.4308755752</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="9">
         <v>34647</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="9">
         <v>27999</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="9">
         <v>6648</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="9">
         <v>0.80812191531734345</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="9">
         <v>0.19187808468265649</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J16" s="9">
         <v>4462</v>
       </c>
-      <c r="K16" s="10">
+      <c r="K16" s="9">
         <v>0.12878459895517649</v>
       </c>
-      <c r="L16" s="10">
+      <c r="L16" s="9">
         <v>23</v>
       </c>
-      <c r="M16" s="10">
+      <c r="M16" s="9">
         <v>6.6383813894420871E-4</v>
       </c>
-      <c r="N16" s="10">
+      <c r="N16" s="9">
         <v>21977</v>
       </c>
-      <c r="O16" s="10">
+      <c r="O16" s="9">
         <v>0.63431177302508157</v>
       </c>
-      <c r="P16" s="10">
+      <c r="P16" s="9">
         <v>8185</v>
       </c>
-      <c r="Q16" s="10">
+      <c r="Q16" s="9">
         <v>0.2362397898807978</v>
       </c>
-      <c r="R16" s="10">
+      <c r="R16" s="9">
         <v>116577.7516379485</v>
       </c>
-      <c r="S16" s="10">
+      <c r="S16" s="9">
         <v>55925.983723522862</v>
       </c>
-      <c r="T16" s="10">
+      <c r="T16" s="9">
         <v>34136.709742002997</v>
       </c>
-      <c r="U16" s="10">
+      <c r="U16" s="9">
         <v>78400.214416615767</v>
       </c>
-      <c r="V16" s="10">
+      <c r="V16" s="9">
         <v>47414.098161456983</v>
       </c>
-      <c r="W16" s="10">
+      <c r="W16" s="9">
         <v>76325.984061479568</v>
       </c>
-      <c r="X16" s="10">
+      <c r="X16" s="9">
         <v>1933640335360</v>
       </c>
-      <c r="Y16" s="10">
+      <c r="Y16" s="9">
         <v>25333972</v>
       </c>
-      <c r="Z16" s="10">
+      <c r="Z16" s="9">
         <v>17520000</v>
       </c>
-      <c r="AA16" s="10">
+      <c r="AA16" s="9">
         <v>2111164.333333333</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <v>4164940526</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="9">
         <v>142</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <v>29330567.084507041</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <v>23580</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="9">
         <v>17033</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="9">
         <v>6547</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="9">
         <v>0.72234944868532658</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="9">
         <v>0.27765055131467348</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="9">
         <v>3918</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="9">
         <v>0.16615776081424941</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L17" s="9">
         <v>26</v>
       </c>
-      <c r="M17" s="10">
+      <c r="M17" s="9">
         <v>1.1026293469041559E-3</v>
       </c>
-      <c r="N17" s="10">
+      <c r="N17" s="9">
         <v>12521</v>
       </c>
-      <c r="O17" s="10">
+      <c r="O17" s="9">
         <v>0.53100084817642068</v>
       </c>
-      <c r="P17" s="10">
+      <c r="P17" s="9">
         <v>7115</v>
       </c>
-      <c r="Q17" s="10">
+      <c r="Q17" s="9">
         <v>0.3017387616624258</v>
       </c>
-      <c r="R17" s="10">
+      <c r="R17" s="9">
         <v>176630.21738761661</v>
       </c>
-      <c r="S17" s="10">
+      <c r="S17" s="9">
         <v>78682.939401622716</v>
       </c>
-      <c r="T17" s="10">
+      <c r="T17" s="9">
         <v>41016.039373851927</v>
       </c>
-      <c r="U17" s="10">
+      <c r="U17" s="9">
         <v>99392.272803935353</v>
       </c>
-      <c r="V17" s="10">
+      <c r="V17" s="9">
         <v>64930.592536047501</v>
       </c>
-      <c r="W17" s="10">
+      <c r="W17" s="9">
         <v>25539.73281955719</v>
       </c>
-      <c r="X17" s="10">
+      <c r="X17" s="9">
         <v>778700259328</v>
       </c>
-      <c r="Y17" s="10">
+      <c r="Y17" s="9">
         <v>30489758</v>
       </c>
-      <c r="Z17" s="10">
+      <c r="Z17" s="9">
         <v>19200000</v>
       </c>
-      <c r="AA17" s="10">
+      <c r="AA17" s="9">
         <v>2540813.166666667</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <v>1673660110</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="9">
         <v>275</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <v>6086036.7636363637</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="9">
         <v>16841</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="9">
         <v>13177</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="9">
         <v>3664</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="9">
         <v>0.78243572234427883</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="9">
         <v>0.21756427765572109</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="9">
         <v>3449</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K18" s="9">
         <v>0.20479781485660001</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="9">
         <v>25</v>
       </c>
-      <c r="M18" s="10">
+      <c r="M18" s="9">
         <v>1.4844724185024639E-3</v>
       </c>
-      <c r="N18" s="10">
+      <c r="N18" s="9">
         <v>8427</v>
       </c>
-      <c r="O18" s="10">
+      <c r="O18" s="9">
         <v>0.50038596282881065</v>
       </c>
-      <c r="P18" s="10">
+      <c r="P18" s="9">
         <v>4940</v>
       </c>
-      <c r="Q18" s="10">
+      <c r="Q18" s="9">
         <v>0.29333174989608701</v>
       </c>
-      <c r="R18" s="10">
+      <c r="R18" s="9">
         <v>99380.090849712011</v>
       </c>
-      <c r="S18" s="10">
+      <c r="S18" s="9">
         <v>55376.390903857216</v>
       </c>
-      <c r="T18" s="10">
+      <c r="T18" s="9">
         <v>34815.02622522843</v>
       </c>
-      <c r="U18" s="10">
+      <c r="U18" s="9">
         <v>76446.975910931171</v>
       </c>
-      <c r="V18" s="10">
+      <c r="V18" s="9">
         <v>51268.443976010924</v>
       </c>
-      <c r="W18" s="10">
+      <c r="W18" s="9">
         <v>17297.38198184967</v>
       </c>
-      <c r="X18" s="10">
+      <c r="X18" s="9">
         <v>528142041088</v>
       </c>
-      <c r="Y18" s="10">
+      <c r="Y18" s="9">
         <v>30533062</v>
       </c>
-      <c r="Z18" s="10">
+      <c r="Z18" s="9">
         <v>21600000</v>
       </c>
-      <c r="AA18" s="10">
+      <c r="AA18" s="9">
         <v>2544421.833333333</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <v>778514487</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <v>112</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <v>6951022.2053571427</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="9">
         <v>10463</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="9">
         <v>7821</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="9">
         <v>2642</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="9">
         <v>0.74749115932332988</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="9">
         <v>0.25250884067667018</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="9">
         <v>1515</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K19" s="9">
         <v>0.1447959476249642</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="9">
         <v>13</v>
       </c>
-      <c r="M19" s="10">
+      <c r="M19" s="9">
         <v>1.24247347796999E-3</v>
       </c>
-      <c r="N19" s="10">
+      <c r="N19" s="9">
         <v>7110</v>
       </c>
-      <c r="O19" s="10">
+      <c r="O19" s="9">
         <v>0.67953741756666353</v>
       </c>
-      <c r="P19" s="10">
+      <c r="P19" s="9">
         <v>1825</v>
       </c>
-      <c r="Q19" s="10">
+      <c r="Q19" s="9">
         <v>0.17442416133040239</v>
       </c>
-      <c r="R19" s="10">
+      <c r="R19" s="9">
         <v>74406.430947147092</v>
       </c>
-      <c r="S19" s="10">
+      <c r="S19" s="9">
         <v>51782.628272251313</v>
       </c>
-      <c r="T19" s="10">
+      <c r="T19" s="9">
         <v>34573.440365682138</v>
       </c>
-      <c r="U19" s="10">
+      <c r="U19" s="9">
         <v>77064.286027397262</v>
       </c>
-      <c r="V19" s="10">
+      <c r="V19" s="9">
         <v>44498.073401510082</v>
       </c>
-      <c r="W19" s="10">
+      <c r="W19" s="9">
         <v>19541.168630599979</v>
       </c>
-      <c r="X19" s="10">
+      <c r="X19" s="9">
         <v>499135021056</v>
       </c>
-      <c r="Y19" s="10">
+      <c r="Y19" s="9">
         <v>25542742</v>
       </c>
-      <c r="Z19" s="10">
+      <c r="Z19" s="9">
         <v>19800000</v>
       </c>
-      <c r="AA19" s="10">
+      <c r="AA19" s="9">
         <v>2128561.833333333</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="9">
         <v>1226916083</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="9">
         <v>32</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <v>38341127.59375</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="9">
         <v>6880</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="9">
         <v>5298</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="9">
         <v>1582</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="9">
         <v>0.77005813953488367</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="9">
         <v>0.2299418604651163</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="9">
         <v>1020</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K20" s="9">
         <v>0.14825581395348841</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="9">
         <v>2</v>
       </c>
-      <c r="M20" s="10">
+      <c r="M20" s="9">
         <v>2.9069767441860459E-4</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="9">
         <v>3549</v>
       </c>
-      <c r="O20" s="10">
+      <c r="O20" s="9">
         <v>0.51584302325581399</v>
       </c>
-      <c r="P20" s="10">
+      <c r="P20" s="9">
         <v>2309</v>
       </c>
-      <c r="Q20" s="10">
+      <c r="Q20" s="9">
         <v>0.33561046511627912</v>
       </c>
-      <c r="R20" s="10">
+      <c r="R20" s="9">
         <v>178330.8260174419</v>
       </c>
-      <c r="S20" s="10">
+      <c r="S20" s="9">
         <v>53935.54109589041</v>
       </c>
-      <c r="T20" s="10">
+      <c r="T20" s="9">
         <v>32285.222316145391</v>
       </c>
-      <c r="U20" s="10">
+      <c r="U20" s="9">
         <v>81563.8328280641</v>
       </c>
-      <c r="V20" s="10">
+      <c r="V20" s="9">
         <v>52039.719040697673</v>
       </c>
-      <c r="W20" s="10">
+      <c r="W20" s="9">
         <v>8611.7141191959381</v>
       </c>
-      <c r="X20" s="10">
+      <c r="X20" s="9">
         <v>200755527680</v>
       </c>
-      <c r="Y20" s="10">
+      <c r="Y20" s="9">
         <v>23311912</v>
       </c>
-      <c r="Z20" s="10">
+      <c r="Z20" s="9">
         <v>18600000</v>
       </c>
-      <c r="AA20" s="10">
+      <c r="AA20" s="9">
         <v>1942659.333333333</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <v>1596628479</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9">
         <v>227</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <v>7033605.6343612336</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="9">
         <v>17096</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="9">
         <v>12168</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="9">
         <v>4928</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="9">
         <v>0.71174543752924657</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="9">
         <v>0.28825456247075337</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J21" s="9">
         <v>1774</v>
       </c>
-      <c r="K21" s="10">
+      <c r="K21" s="9">
         <v>0.1037669630322883</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="9">
         <v>16</v>
       </c>
-      <c r="M21" s="10">
+      <c r="M21" s="9">
         <v>9.3589143659335522E-4</v>
       </c>
-      <c r="N21" s="10">
+      <c r="N21" s="9">
         <v>10033</v>
       </c>
-      <c r="O21" s="10">
+      <c r="O21" s="9">
         <v>0.58686242395882082</v>
       </c>
-      <c r="P21" s="10">
+      <c r="P21" s="9">
         <v>5273</v>
       </c>
-      <c r="Q21" s="10">
+      <c r="Q21" s="9">
         <v>0.30843472157229762</v>
       </c>
-      <c r="R21" s="10">
+      <c r="R21" s="9">
         <v>93391.932557323351</v>
       </c>
-      <c r="S21" s="10">
+      <c r="S21" s="9">
         <v>48610.917877094973</v>
       </c>
-      <c r="T21" s="10">
+      <c r="T21" s="9">
         <v>31952.443636001201</v>
       </c>
-      <c r="U21" s="10">
+      <c r="U21" s="9">
         <v>60515.475251280113</v>
       </c>
-      <c r="V21" s="10">
+      <c r="V21" s="9">
         <v>42506.463968179691</v>
       </c>
-      <c r="W21" s="10">
+      <c r="W21" s="9">
         <v>39759.545756340027</v>
       </c>
-      <c r="X21" s="10">
+      <c r="X21" s="9">
         <v>924450881536</v>
       </c>
-      <c r="Y21" s="10">
+      <c r="Y21" s="9">
         <v>23251042</v>
       </c>
-      <c r="Z21" s="10">
+      <c r="Z21" s="9">
         <v>15600000</v>
       </c>
-      <c r="AA21" s="10">
+      <c r="AA21" s="9">
         <v>1937586.833333333</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="9">
         <v>16290782103</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="9">
         <v>604</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="9">
         <v>26971493.54801324</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="9">
         <v>59219</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="9">
         <v>40451</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="9">
         <v>18768</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="9">
         <v>0.68307468886674882</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="9">
         <v>0.31692531113325118</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="9">
         <v>13240</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="9">
         <v>0.22357689255137711</v>
       </c>
-      <c r="L22" s="10">
+      <c r="L22" s="9">
         <v>84</v>
       </c>
-      <c r="M22" s="10">
+      <c r="M22" s="9">
         <v>1.4184636687549601E-3</v>
       </c>
-      <c r="N22" s="10">
+      <c r="N22" s="9">
         <v>30963</v>
       </c>
-      <c r="O22" s="10">
+      <c r="O22" s="9">
         <v>0.52285584018642661</v>
       </c>
-      <c r="P22" s="10">
+      <c r="P22" s="9">
         <v>14932</v>
       </c>
-      <c r="Q22" s="10">
+      <c r="Q22" s="9">
         <v>0.25214880359344127</v>
       </c>
-      <c r="R22" s="10">
+      <c r="R22" s="9">
         <v>275093.83986558369</v>
       </c>
-      <c r="S22" s="10">
+      <c r="S22" s="9">
         <v>86759.307039927953</v>
       </c>
-      <c r="T22" s="10">
+      <c r="T22" s="9">
         <v>44423.300778348348</v>
       </c>
-      <c r="U22" s="10">
+      <c r="U22" s="9">
         <v>79599.441066166619</v>
       </c>
-      <c r="V22" s="10">
+      <c r="V22" s="9">
         <v>62818.327276718621</v>
       </c>
-      <c r="W22" s="10">
+      <c r="W22" s="9">
         <v>29384.831278324131</v>
       </c>
-      <c r="X22" s="10">
+      <c r="X22" s="9">
         <v>842796105728</v>
       </c>
-      <c r="Y22" s="10">
+      <c r="Y22" s="9">
         <v>28681332</v>
       </c>
-      <c r="Z22" s="10">
+      <c r="Z22" s="9">
         <v>17760000</v>
       </c>
-      <c r="AA22" s="10">
+      <c r="AA22" s="9">
         <v>2390111</v>
       </c>
     </row>
